--- a/examples/example_continuous_errors_results.xlsx
+++ b/examples/example_continuous_errors_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="144">
   <si>
     <t>Group</t>
   </si>
@@ -194,22 +194,22 @@
     <t>Weighting of Eyes (mean-loss metrics)</t>
   </si>
   <si>
-    <t>Mean Error (MPE) Test</t>
-  </si>
-  <si>
-    <t>MAE Test</t>
-  </si>
-  <si>
-    <t>RMSE Test</t>
-  </si>
-  <si>
-    <t>MedAE Test</t>
-  </si>
-  <si>
-    <t>SD Test</t>
-  </si>
-  <si>
-    <t>Proportion Within Tolerance Test</t>
+    <t>Mean error Test</t>
+  </si>
+  <si>
+    <t>Mean absolute error Test</t>
+  </si>
+  <si>
+    <t>Root mean squared error Test</t>
+  </si>
+  <si>
+    <t>Median absolute error Test</t>
+  </si>
+  <si>
+    <t>SD of the error Test</t>
+  </si>
+  <si>
+    <t>Proportion within tolerance Test</t>
   </si>
   <si>
     <t>Tolerance (proportion within)</t>
@@ -230,6 +230,9 @@
     <t>Subgroups</t>
   </si>
   <si>
+    <t>Subgroup adjustment</t>
+  </si>
+  <si>
     <t>Patient as the unit (cluster bootstrap / cluster-robust tests)</t>
   </si>
   <si>
@@ -254,21 +257,27 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean Error (MPE), MAE, RMSE, MedAE, SD; Hommel: Proportion Within Tolerance</t>
-  </si>
-  <si>
-    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean Error (MPE), MAE, MedAE; Bonferroni (percentile bootstrap): RMSE, SD, Proportion Within Tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean error, Mean absolute error, Root mean squared error, Median absolute error, SD of the error; Hommel: Proportion within tolerance</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean error, Mean absolute error, Median absolute error; Bonferroni (percentile bootstrap): Root mean squared error, SD of the error, Proportion within tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
   </si>
   <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
-    <t>axial_length, continuous, cut points 22, 24.5: &lt;22, 22 to &lt;24.5, &gt;=24.5 (each interval includes its lower cut point). Each subgroup is analyzed separately with the same models, tests and settings; p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
+    <t>axial_length, continuous, cut points 22, 24.5: &lt;22, 22 to &lt;24.5, &gt;=24.5 (each interval includes its lower cut point). Each subgroup is analyzed separately with the same models, tests and settings</t>
+  </si>
+  <si>
+    <t>Subgroup results are exploratory: p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
+    <t>grouping</t>
+  </si>
+  <si>
     <t>model</t>
   </si>
   <si>
@@ -291,6 +300,9 @@
   </si>
   <si>
     <t>method</t>
+  </si>
+  <si>
+    <t>axial_length</t>
   </si>
   <si>
     <t>bias</t>
@@ -2652,7 +2664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -2672,7 +2684,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2680,7 +2692,7 @@
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2688,7 +2700,7 @@
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2696,7 +2708,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2704,7 +2716,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2712,7 +2724,7 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2720,7 +2732,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2728,7 +2740,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2736,7 +2748,7 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2744,7 +2756,7 @@
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2752,7 +2764,7 @@
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2760,7 +2772,7 @@
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2768,7 +2780,7 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2776,7 +2788,15 @@
         <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2786,2127 +2806,2346 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="18.7109375" customWidth="1"/>
+    <col min="1" max="10" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>92</v>
+      </c>
+      <c r="J1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2">
         <v>0.02049261083743842</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>-0.03627408686752381</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.07817344322344316</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>406</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>250</v>
       </c>
-      <c r="I2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>47</v>
       </c>
       <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3">
         <v>0.02807881773399015</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>-0.03130163576219235</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.08814663182346119</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>406</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>250</v>
       </c>
-      <c r="I3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>47</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
         <v>53</v>
       </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4">
         <v>0.04536945812807881</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>-0.02279186728395061</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.1117210615626027</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>406</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>250</v>
       </c>
-      <c r="I4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>47</v>
       </c>
       <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
         <v>51</v>
       </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5">
         <v>0.4010837438423646</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.3695515125104408</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.4314988474459895</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>406</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>250</v>
       </c>
-      <c r="I5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>47</v>
       </c>
       <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="C6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6">
         <v>0.413743842364532</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.382458068528919</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.4454042263674867</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>406</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>250</v>
       </c>
-      <c r="I6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>47</v>
       </c>
       <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7">
         <v>0.4725615763546798</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.4363228203517588</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.5081824833702879</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>406</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>250</v>
       </c>
-      <c r="I7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8">
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8">
         <v>0.503346436828533</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.4673413351028322</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.5381596977405827</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>406</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>250</v>
       </c>
-      <c r="I8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>47</v>
       </c>
       <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9">
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9">
         <v>0.5190271308530763</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.4829163917076886</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.5537674085132629</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>406</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>250</v>
       </c>
-      <c r="I9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>47</v>
       </c>
       <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10">
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10">
         <v>0.5875820873372553</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.5463605798821268</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.6266470149182913</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>406</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>250</v>
       </c>
-      <c r="I10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>47</v>
       </c>
       <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11">
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11">
         <v>0.34</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.3</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.38</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>406</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>250</v>
       </c>
-      <c r="I11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>47</v>
       </c>
       <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
         <v>52</v>
       </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12">
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12">
         <v>0.35</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.31</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.4</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>406</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>250</v>
       </c>
-      <c r="I12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>47</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
         <v>53</v>
       </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13">
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13">
         <v>0.4</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.36</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.45</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>406</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>250</v>
       </c>
-      <c r="I13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>47</v>
       </c>
       <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14">
+      <c r="D14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14">
         <v>0.5035496260262651</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.4670729663895485</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.5373554039329193</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>406</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>250</v>
       </c>
-      <c r="I14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>47</v>
       </c>
       <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15">
+      <c r="D15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15">
         <v>0.5189064985777815</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.4812686049790749</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.5530250723007292</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>406</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>250</v>
       </c>
-      <c r="I15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>47</v>
       </c>
       <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
         <v>53</v>
       </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16">
+      <c r="D16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16">
         <v>0.5865506926221365</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.5442726547777094</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.624844231822534</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>406</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>250</v>
       </c>
-      <c r="I16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>47</v>
       </c>
       <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>51</v>
       </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17">
+      <c r="D17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17">
         <v>0.6921182266009852</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.6451574224491374</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.739135938359934</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>406</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>250</v>
       </c>
-      <c r="I17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>47</v>
       </c>
       <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18">
+      <c r="D18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18">
         <v>0.6576354679802956</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.6104218362282878</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.7064676616915423</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>406</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>250</v>
       </c>
-      <c r="I18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>47</v>
       </c>
       <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
         <v>53</v>
       </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19">
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19">
         <v>0.6133004926108374</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.5623261083560855</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.6649370426527788</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>406</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>250</v>
       </c>
-      <c r="I19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
         <v>51</v>
       </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20">
         <v>0.01043478260869565</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-0.1405866818558409</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.1541802941812676</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>69</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>44</v>
       </c>
-      <c r="I20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
         <v>52</v>
       </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21">
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21">
         <v>0.01811594202898551</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>-0.1240307692307692</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.1600074626865672</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>69</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>44</v>
       </c>
-      <c r="I21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22">
+      <c r="D22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22">
         <v>0.06304347826086956</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-0.08418067556952083</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.20672519160952</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>69</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>44</v>
       </c>
-      <c r="I22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>48</v>
       </c>
       <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23">
+      <c r="D23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23">
         <v>0.4165217391304348</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.3406073426573427</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.4958143892339545</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>69</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>44</v>
       </c>
-      <c r="I23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24">
+      <c r="D24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24">
         <v>0.4256521739130435</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.3438439869989167</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.5062345755693584</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>69</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>44</v>
       </c>
-      <c r="I24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
         <v>53</v>
       </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25">
         <v>0.4534782608695653</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.3886563130294475</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.5249209799861974</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>69</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>44</v>
       </c>
-      <c r="I25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26">
         <v>0.5201170436838566</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.4284678805213774</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.6072271720564225</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>69</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>44</v>
       </c>
-      <c r="I26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
         <v>52</v>
       </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27">
         <v>0.5374321662622487</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.4330597529790759</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.6319503432093759</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>69</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>44</v>
       </c>
-      <c r="I27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" t="s">
         <v>53</v>
       </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28">
         <v>0.5544640969283843</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.4730864484316748</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.6373175941800167</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>69</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>44</v>
       </c>
-      <c r="I28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
         <v>51</v>
       </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29">
+      <c r="D29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29">
         <v>0.36</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.3</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.45</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>69</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>44</v>
       </c>
-      <c r="I29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
         <v>52</v>
       </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30">
         <v>0.35</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.29</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.46</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>69</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>44</v>
       </c>
-      <c r="I30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
         <v>53</v>
       </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31">
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31">
         <v>0.4</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.31</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.48</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>69</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>44</v>
       </c>
-      <c r="I31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>48</v>
       </c>
       <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
         <v>51</v>
       </c>
-      <c r="C32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32">
+      <c r="D32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32">
         <v>0.5238220251826913</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.425397438980178</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.605553217988143</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>69</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>44</v>
       </c>
-      <c r="I32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="J32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>48</v>
       </c>
       <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
         <v>52</v>
       </c>
-      <c r="C33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33">
         <v>0.5410617974988647</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.4317391992536254</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.6309148172084375</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>69</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>44</v>
       </c>
-      <c r="I33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>48</v>
       </c>
       <c r="B34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" t="s">
         <v>53</v>
       </c>
-      <c r="C34" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34">
+      <c r="D34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34">
         <v>0.5549040837833944</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.4665901674614412</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.6374200101169525</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>69</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>44</v>
       </c>
-      <c r="I34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>48</v>
       </c>
       <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
         <v>51</v>
       </c>
-      <c r="C35" t="s">
-        <v>96</v>
-      </c>
-      <c r="D35">
+      <c r="D35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.5384615384615384</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.7910447761194029</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>69</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>44</v>
       </c>
-      <c r="I35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="J35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
         <v>52</v>
       </c>
-      <c r="C36" t="s">
-        <v>96</v>
-      </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36">
         <v>0.7101449275362319</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.5966456287985042</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.8235294117647058</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>69</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>44</v>
       </c>
-      <c r="I36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" t="s">
         <v>53</v>
       </c>
-      <c r="C37" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37">
         <v>0.6521739130434783</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.5373134328358209</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.7647058823529411</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>69</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>44</v>
       </c>
-      <c r="I37" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="J37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" t="s">
         <v>51</v>
       </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38">
         <v>0.01693277310924369</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>-0.05493833289554333</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.0878347802546582</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>238</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>154</v>
       </c>
-      <c r="I38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>49</v>
       </c>
       <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" t="s">
         <v>52</v>
       </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39">
+      <c r="D39" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39">
         <v>0.01974789915966386</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-0.05385132514544282</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.09216067119220821</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>238</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>154</v>
       </c>
-      <c r="I39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="J39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40">
         <v>0.01130252100840337</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>-0.07513349699945444</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.09668995796523235</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>238</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>154</v>
       </c>
-      <c r="I40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="J40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>49</v>
       </c>
       <c r="B41" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" t="s">
         <v>51</v>
       </c>
-      <c r="C41" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41">
         <v>0.3740756302521008</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.3347098884618991</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.4146456049655938</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>238</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>154</v>
       </c>
-      <c r="I41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
         <v>52</v>
       </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42">
+      <c r="D42" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42">
         <v>0.3876470588235295</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.3476754384342164</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.4285869397759103</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>238</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>154</v>
       </c>
-      <c r="I42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="J42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" t="s">
         <v>53</v>
       </c>
-      <c r="C43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43">
+      <c r="D43" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43">
         <v>0.4584453781512605</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0.4111537670148784</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>0.5100834219858156</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>238</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>154</v>
       </c>
-      <c r="I43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
         <v>51</v>
       </c>
-      <c r="C44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44">
+      <c r="D44" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44">
         <v>0.4805271090386144</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.4319239833622951</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.5290570429882944</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>238</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>154</v>
       </c>
-      <c r="I44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="J44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
         <v>52</v>
       </c>
-      <c r="C45" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45">
+      <c r="D45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45">
         <v>0.4957262730732819</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.4490506933811403</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.5432667880392282</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>238</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>154</v>
       </c>
-      <c r="I45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="J45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" t="s">
-        <v>93</v>
-      </c>
-      <c r="D46">
+      <c r="D46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46">
         <v>0.5806744123080022</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.5258431036973865</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.6349583666787159</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>238</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>154</v>
       </c>
-      <c r="I46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="J46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
         <v>51</v>
       </c>
-      <c r="C47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47">
+      <c r="D47" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47">
         <v>0.29</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.24</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.36</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>238</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>154</v>
       </c>
-      <c r="I47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="J47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" t="s">
         <v>52</v>
       </c>
-      <c r="C48" t="s">
-        <v>94</v>
-      </c>
-      <c r="D48">
+      <c r="D48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48">
         <v>0.335</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.27</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.39</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>238</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>154</v>
       </c>
-      <c r="I48" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="J48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
         <v>53</v>
       </c>
-      <c r="C49" t="s">
-        <v>94</v>
-      </c>
-      <c r="D49">
+      <c r="D49" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49">
         <v>0.37</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.3</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>0.44</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>238</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>154</v>
       </c>
-      <c r="I49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="J49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50">
+      <c r="D50" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50">
         <v>0.4812407527715649</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.4319931836210766</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>0.5277549495812133</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>238</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>154</v>
       </c>
-      <c r="I50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="J50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51">
+      <c r="D51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51">
         <v>0.4963766811552734</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.4481946743754427</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>0.5425005845529751</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>238</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>154</v>
       </c>
-      <c r="I51" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="J51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52">
+      <c r="D52" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52">
         <v>0.581787933214607</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.5249154479852544</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>0.6342739322681901</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>238</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>154</v>
       </c>
-      <c r="I52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="J52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>49</v>
       </c>
       <c r="B53" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" t="s">
         <v>51</v>
       </c>
-      <c r="C53" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53">
         <v>0.7394957983193278</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.680672268907563</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0.7949842238836683</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>238</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>154</v>
       </c>
-      <c r="I53" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="J53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" t="s">
         <v>52</v>
       </c>
-      <c r="C54" t="s">
-        <v>96</v>
-      </c>
-      <c r="D54">
+      <c r="D54" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54">
         <v>0.6764705882352942</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.6147030229657349</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>0.7364016736401674</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>238</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>154</v>
       </c>
-      <c r="I54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="J54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" t="s">
         <v>53</v>
       </c>
-      <c r="C55" t="s">
-        <v>96</v>
-      </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55">
         <v>0.6386554621848739</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.5665236051502146</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>0.7024793388429752</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>238</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>154</v>
       </c>
-      <c r="I55" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="J55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>50</v>
       </c>
       <c r="B56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
         <v>51</v>
       </c>
-      <c r="C56" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56">
+      <c r="D56" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56">
         <v>0.03606060606060607</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>-0.08726458333333333</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>0.158636274509804</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>99</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>64</v>
       </c>
-      <c r="I56" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="J56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>50</v>
       </c>
       <c r="B57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" t="s">
         <v>52</v>
       </c>
-      <c r="C57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57">
+      <c r="D57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57">
         <v>0.05505050505050505</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>-0.07600303030303028</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>0.1818428361035136</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>99</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>64</v>
       </c>
-      <c r="I57" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+      <c r="J57" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>50</v>
       </c>
       <c r="B58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" t="s">
         <v>53</v>
       </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
-      <c r="D58">
+      <c r="D58" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58">
         <v>0.1149494949494949</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>-0.02216176470588235</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>0.249908653846154</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>99</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>64</v>
       </c>
-      <c r="I58" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+      <c r="J58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>50</v>
       </c>
       <c r="B59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" t="s">
         <v>51</v>
       </c>
-      <c r="C59" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59">
+      <c r="D59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59">
         <v>0.4552525252525252</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>0.3999027669902913</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>0.5174239953713444</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>99</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>64</v>
       </c>
-      <c r="I59" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+      <c r="J59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>50</v>
       </c>
       <c r="B60" t="s">
+        <v>94</v>
+      </c>
+      <c r="C60" t="s">
         <v>52</v>
       </c>
-      <c r="C60" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60">
+      <c r="D60" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60">
         <v>0.4681818181818182</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>0.40969840430645</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>0.5268939379787034</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>99</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>64</v>
       </c>
-      <c r="I60" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+      <c r="J60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>50</v>
       </c>
       <c r="B61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C61" t="s">
         <v>53</v>
       </c>
-      <c r="C61" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61">
+      <c r="D61" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61">
         <v>0.5197979797979798</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>0.449176170212766</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>0.5939079702970298</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>99</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>64</v>
       </c>
-      <c r="I61" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+      <c r="J61" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>50</v>
       </c>
       <c r="B62" t="s">
+        <v>94</v>
+      </c>
+      <c r="C62" t="s">
         <v>51</v>
       </c>
-      <c r="C62" t="s">
-        <v>93</v>
-      </c>
-      <c r="D62">
+      <c r="D62" t="s">
+        <v>97</v>
+      </c>
+      <c r="E62">
         <v>0.543478322353971</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>0.4817497049522778</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>0.6083533319636707</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>99</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>64</v>
       </c>
-      <c r="I62" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+      <c r="J62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>50</v>
       </c>
       <c r="B63" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" t="s">
         <v>52</v>
       </c>
-      <c r="C63" t="s">
-        <v>93</v>
-      </c>
-      <c r="D63">
+      <c r="D63" t="s">
+        <v>97</v>
+      </c>
+      <c r="E63">
         <v>0.559177787452075</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>0.4971917299145414</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>0.6172601740831101</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>99</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>64</v>
       </c>
-      <c r="I63" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+      <c r="J63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>50</v>
       </c>
       <c r="B64" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" t="s">
         <v>53</v>
       </c>
-      <c r="C64" t="s">
-        <v>93</v>
-      </c>
-      <c r="D64">
+      <c r="D64" t="s">
+        <v>97</v>
+      </c>
+      <c r="E64">
         <v>0.6253112356372157</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>0.5432590730716428</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>0.7045706765071336</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>99</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>64</v>
       </c>
-      <c r="I64" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+      <c r="J64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>50</v>
       </c>
       <c r="B65" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" t="s">
         <v>51</v>
       </c>
-      <c r="C65" t="s">
-        <v>94</v>
-      </c>
-      <c r="D65">
+      <c r="D65" t="s">
+        <v>98</v>
+      </c>
+      <c r="E65">
         <v>0.45</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>0.36</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>0.49</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>99</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>64</v>
       </c>
-      <c r="I65" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="J65" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>50</v>
       </c>
       <c r="B66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C66" t="s">
         <v>52</v>
       </c>
-      <c r="C66" t="s">
-        <v>94</v>
-      </c>
-      <c r="D66">
+      <c r="D66" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66">
         <v>0.44</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>0.33</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>0.54</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>99</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>64</v>
       </c>
-      <c r="I66" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+      <c r="J66" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>50</v>
       </c>
       <c r="B67" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" t="s">
         <v>53</v>
       </c>
-      <c r="C67" t="s">
-        <v>94</v>
-      </c>
-      <c r="D67">
+      <c r="D67" t="s">
+        <v>98</v>
+      </c>
+      <c r="E67">
         <v>0.49</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>0.39</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>0.53</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>99</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>64</v>
       </c>
-      <c r="I67" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+      <c r="J67" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>50</v>
       </c>
       <c r="B68" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" t="s">
         <v>51</v>
       </c>
-      <c r="C68" t="s">
-        <v>95</v>
-      </c>
-      <c r="D68">
+      <c r="D68" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68">
         <v>0.5450403807953941</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>0.4784080911106443</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>0.6054111907182181</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>99</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>64</v>
       </c>
-      <c r="I68" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+      <c r="J68" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>50</v>
       </c>
       <c r="B69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" t="s">
         <v>52</v>
       </c>
-      <c r="C69" t="s">
-        <v>95</v>
-      </c>
-      <c r="D69">
+      <c r="D69" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69">
         <v>0.5592932379303726</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>0.4907488224673515</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>0.6162487836377396</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>99</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>64</v>
       </c>
-      <c r="I69" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="J69" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>50</v>
       </c>
       <c r="B70" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" t="s">
         <v>53</v>
       </c>
-      <c r="C70" t="s">
-        <v>95</v>
-      </c>
-      <c r="D70">
+      <c r="D70" t="s">
+        <v>99</v>
+      </c>
+      <c r="E70">
         <v>0.6177830240223103</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>0.5390617375857683</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>0.6882910415358988</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>99</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>64</v>
       </c>
-      <c r="I70" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+      <c r="J70" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>50</v>
       </c>
       <c r="B71" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" t="s">
         <v>51</v>
       </c>
-      <c r="C71" t="s">
-        <v>96</v>
-      </c>
-      <c r="D71">
+      <c r="D71" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71">
         <v>0.5959595959595959</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>0.5</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>0.684802737520129</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>99</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>64</v>
       </c>
-      <c r="I71" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+      <c r="J71" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>50</v>
       </c>
       <c r="B72" t="s">
+        <v>94</v>
+      </c>
+      <c r="C72" t="s">
         <v>52</v>
       </c>
-      <c r="C72" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72">
+      <c r="D72" t="s">
+        <v>100</v>
+      </c>
+      <c r="E72">
         <v>0.5757575757575758</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>0.4838347227256253</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>0.67</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>99</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>64</v>
       </c>
-      <c r="I72" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+      <c r="J72" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>50</v>
       </c>
       <c r="B73" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" t="s">
         <v>53</v>
       </c>
-      <c r="C73" t="s">
-        <v>96</v>
-      </c>
-      <c r="D73">
+      <c r="D73" t="s">
+        <v>100</v>
+      </c>
+      <c r="E73">
         <v>0.5252525252525253</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>0.4210526315789473</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>0.6263220439691031</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>99</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>64</v>
       </c>
-      <c r="I73" t="s">
-        <v>97</v>
+      <c r="J73" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4916,1214 +5155,1280 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="12" width="18.7109375" customWidth="1"/>
-    <col min="13" max="13" width="36.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="36.7109375" customWidth="1"/>
-    <col min="16" max="17" width="18.7109375" customWidth="1"/>
-    <col min="18" max="18" width="36.7109375" customWidth="1"/>
+    <col min="1" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="36.7109375" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="36.7109375" customWidth="1"/>
+    <col min="17" max="18" width="18.7109375" customWidth="1"/>
+    <col min="19" max="19" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="K1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="R1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>114</v>
+      </c>
+      <c r="S1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.02049261083743842</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.02807881773399015</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>-0.007586206896551734</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>-0.04493901095487556</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.03040411335473117</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.6926</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.07912915589624739</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1.530907631213612</v>
       </c>
-      <c r="M2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2">
         <v>0.7454</v>
       </c>
-      <c r="O2" t="s">
-        <v>112</v>
-      </c>
-      <c r="P2">
+      <c r="P2" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q2">
         <v>-0.05410272103966406</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>0.03893030724656057</v>
       </c>
-      <c r="R2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="S2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.4010837438423646</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.413743842364532</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>-0.01266009852216748</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>-0.04537308813124185</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.0208441631385477</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.461</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.1505359768729156</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1.455610834346575</v>
       </c>
-      <c r="M3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3">
+      <c r="N3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3">
         <v>0.461</v>
       </c>
-      <c r="O3" t="s">
-        <v>112</v>
-      </c>
-      <c r="P3">
+      <c r="P3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3">
         <v>-0.05229618964656447</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>0.02697599260222917</v>
       </c>
-      <c r="R3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="S3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>52</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.503346436828533</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.5190271308530763</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>-0.01568069402454331</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>-0.05106318963604003</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.01787937336349218</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.3852</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.08402553829771155</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1.525496624127441</v>
       </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-      <c r="N4">
+      <c r="N4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4">
         <v>0.3852</v>
       </c>
-      <c r="O4" t="s">
-        <v>112</v>
-      </c>
-      <c r="P4">
+      <c r="P4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q4">
         <v>-0.05856576544801699</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>0.02781683152088923</v>
       </c>
-      <c r="R4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="S4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>52</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.34</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.35</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>-0.009999999999999953</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.03999999999999998</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.6968</v>
       </c>
-      <c r="M5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N5">
+      <c r="N5" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5">
         <v>0.844</v>
       </c>
-      <c r="O5" t="s">
-        <v>112</v>
-      </c>
-      <c r="P5">
+      <c r="P5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q5">
         <v>-0.08000000000000002</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>0.06000000000000011</v>
       </c>
-      <c r="R5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>52</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.5035496260262651</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.5189064985777815</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>-0.01535687255151641</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>-0.05064189418206674</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.01876017330561083</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.3894</v>
       </c>
-      <c r="M6" t="s">
-        <v>74</v>
-      </c>
-      <c r="N6">
+      <c r="N6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O6">
         <v>0.3894</v>
       </c>
-      <c r="O6" t="s">
-        <v>112</v>
-      </c>
-      <c r="P6">
+      <c r="P6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q6">
         <v>-0.05815433485882694</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>0.02825025172545625</v>
       </c>
-      <c r="R6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.6921182266009852</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.6576354679802956</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.03448275862068961</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-0.01805205348027686</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.08780487804878048</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.204560421762222</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.04018448296617311</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1.575352047426485</v>
       </c>
-      <c r="M7" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7">
+      <c r="N7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7">
         <v>0.204560421762222</v>
       </c>
-      <c r="O7" t="s">
-        <v>113</v>
-      </c>
-      <c r="P7">
+      <c r="P7" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7">
         <v>-0.03189014549308666</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>0.09762516046213096</v>
       </c>
-      <c r="R7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>53</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.02049261083743842</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.04536945812807881</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>-0.02487684729064039</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>-0.07516438999171443</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.02555545062902334</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.323</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.1112429598342346</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1.496102394400772</v>
       </c>
-      <c r="M8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N8">
+      <c r="N8" t="s">
+        <v>73</v>
+      </c>
+      <c r="O8">
         <v>0.5734</v>
       </c>
-      <c r="O8" t="s">
-        <v>112</v>
-      </c>
-      <c r="P8">
+      <c r="P8" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q8">
         <v>-0.08440726271056505</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>0.03465356812928412</v>
       </c>
-      <c r="R8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>53</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.4010837438423646</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.4725615763546798</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>-0.07147783251231526</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>-0.1094511309795231</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>-0.03377935695481713</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.0004</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.05897836845261967</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>1.553586372596406</v>
       </c>
-      <c r="M9" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9">
+      <c r="N9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9">
         <v>0.0004</v>
       </c>
-      <c r="O9" t="s">
-        <v>112</v>
-      </c>
-      <c r="P9">
+      <c r="P9" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q9">
         <v>-0.1160939316204946</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>-0.02686173340413649</v>
       </c>
-      <c r="R9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>53</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.503346436828533</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.5875820873372553</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-0.08423565050872228</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>-0.1255427629627515</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-0.0419672383242247</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.0004</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.03487850112907201</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>1.581607874494274</v>
       </c>
-      <c r="M10" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10">
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10">
         <v>0.0008</v>
       </c>
-      <c r="O10" t="s">
-        <v>112</v>
-      </c>
-      <c r="P10">
+      <c r="P10" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q10">
         <v>-0.1343146850892963</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>-0.03239054644227168</v>
       </c>
-      <c r="R10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="S10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>53</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.34</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.4</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>-0.06</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>-0.12</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>-0.009999999999999953</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.0392</v>
       </c>
-      <c r="M11" t="s">
-        <v>73</v>
-      </c>
-      <c r="N11">
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11">
         <v>0.09859999999999999</v>
       </c>
-      <c r="O11" t="s">
-        <v>112</v>
-      </c>
-      <c r="P11">
+      <c r="P11" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q11">
         <v>-0.1280741611297382</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>0.008074161129738258</v>
       </c>
-      <c r="R11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>53</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.5035496260262651</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.5865506926221365</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-0.08300106659587148</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>-0.124012759523577</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-0.04070333062114999</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="M12" t="s">
-        <v>74</v>
-      </c>
-      <c r="N12">
+      <c r="N12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12">
         <v>0.0008</v>
       </c>
-      <c r="O12" t="s">
-        <v>112</v>
-      </c>
-      <c r="P12">
+      <c r="P12" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q12">
         <v>-0.1324121069898527</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>-0.03081160526701515</v>
       </c>
-      <c r="R12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>53</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.6921182266009852</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.6133004926108374</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.0788177339901478</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.01979710286299567</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.1380185633575464</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.009022063055144957</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.09523875150218851</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1.513247813472457</v>
       </c>
-      <c r="M13" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13">
+      <c r="N13" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13">
         <v>0.02706618916543487</v>
       </c>
-      <c r="O13" t="s">
-        <v>113</v>
-      </c>
-      <c r="P13">
+      <c r="P13" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q13">
         <v>0.005016331658291476</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>0.1509315375982046</v>
       </c>
-      <c r="R13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>53</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.02807881773399015</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.04536945812807881</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>-0.01729064039408866</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>-0.07150679591982637</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.03668306575040802</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.518</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.1843641333656314</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1.422466582636034</v>
       </c>
-      <c r="M14" t="s">
-        <v>72</v>
-      </c>
-      <c r="N14">
+      <c r="N14" t="s">
+        <v>73</v>
+      </c>
+      <c r="O14">
         <v>0.7454</v>
       </c>
-      <c r="O14" t="s">
-        <v>112</v>
-      </c>
-      <c r="P14">
+      <c r="P14" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q14">
         <v>-0.08180644473769276</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>0.0472251639495153</v>
       </c>
-      <c r="R14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>53</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.413743842364532</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.4725615763546798</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>-0.05881773399014778</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-0.1025986784782056</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>-0.01794955791900317</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.005</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.187351608726497</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>1.419611895158891</v>
       </c>
-      <c r="M15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15">
+      <c r="N15" t="s">
+        <v>73</v>
+      </c>
+      <c r="O15">
         <v>0.0104</v>
       </c>
-      <c r="O15" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15">
+      <c r="P15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q15">
         <v>-0.1084139624854691</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>-0.009221505494826733</v>
       </c>
-      <c r="R15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="S15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.5190271308530763</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.5875820873372553</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-0.06855495648417897</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-0.1131287403553188</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-0.02214090274061026</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.0036</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.103144323905025</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>1.504729680828269</v>
       </c>
-      <c r="M16" t="s">
-        <v>72</v>
-      </c>
-      <c r="N16">
+      <c r="N16" t="s">
+        <v>73</v>
+      </c>
+      <c r="O16">
         <v>0.0052</v>
       </c>
-      <c r="O16" t="s">
-        <v>112</v>
-      </c>
-      <c r="P16">
+      <c r="P16" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16">
         <v>-0.1237607966652774</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>-0.01197481543232409</v>
       </c>
-      <c r="R16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="S16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>53</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.35</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.4</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-0.05000000000000004</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>-0.11</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.01000000000000001</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.2012</v>
       </c>
-      <c r="M17" t="s">
-        <v>73</v>
-      </c>
-      <c r="N17">
+      <c r="N17" t="s">
+        <v>74</v>
+      </c>
+      <c r="O17">
         <v>0.2164</v>
       </c>
-      <c r="O17" t="s">
-        <v>112</v>
-      </c>
-      <c r="P17">
+      <c r="P17" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q17">
         <v>-0.1230166690346137</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>0.02301666903461358</v>
       </c>
-      <c r="R17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="S17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
         <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>53</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.5189064985777815</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.5865506926221365</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>-0.06764419404435507</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>-0.1119735373189496</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>-0.0211188354296671</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.005</v>
       </c>
-      <c r="M18" t="s">
-        <v>74</v>
-      </c>
-      <c r="N18">
+      <c r="N18" t="s">
+        <v>75</v>
+      </c>
+      <c r="O18">
         <v>0.008399999999999999</v>
       </c>
-      <c r="O18" t="s">
-        <v>112</v>
-      </c>
-      <c r="P18">
+      <c r="P18" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q18">
         <v>-0.1227389787054995</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>-0.009991811914109227</v>
       </c>
-      <c r="R18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="S18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
         <v>52</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>53</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.6576354679802956</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.6133004926108374</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.04433497536945818</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>-0.01686950701356149</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.1050067237163814</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.1549785601955193</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.181230275610628</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>1.425473510706959</v>
       </c>
-      <c r="M19" t="s">
-        <v>75</v>
-      </c>
-      <c r="N19">
+      <c r="N19" t="s">
+        <v>76</v>
+      </c>
+      <c r="O19">
         <v>0.204560421762222</v>
       </c>
-      <c r="O19" t="s">
-        <v>113</v>
-      </c>
-      <c r="P19">
+      <c r="P19" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q19">
         <v>-0.0304885234225776</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>0.1172132467873379</v>
       </c>
-      <c r="R19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
         <v>51</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>52</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.01043478260869565</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.01811594202898551</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>-0.007681159420289864</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>-0.08681275054350658</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.09128877870612474</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.8618</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.2388921310381965</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>1.336772764287313</v>
       </c>
-      <c r="M20" t="s">
-        <v>72</v>
-      </c>
-      <c r="N20">
+      <c r="N20" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20">
         <v>0.8618</v>
       </c>
-      <c r="O20" t="s">
-        <v>112</v>
-      </c>
-      <c r="P20">
+      <c r="P20" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q20">
         <v>-0.1141871619631026</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>0.09882484312252289</v>
       </c>
-      <c r="R20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.4165217391304348</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.4256521739130435</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>-0.009130434782608721</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>-0.09398305560858214</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.07321618921121935</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.8304</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.3271451061470259</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>1.26766664491409</v>
       </c>
-      <c r="M21" t="s">
-        <v>72</v>
-      </c>
-      <c r="N21">
+      <c r="N21" t="s">
+        <v>73</v>
+      </c>
+      <c r="O21">
         <v>0.8304</v>
       </c>
-      <c r="O21" t="s">
-        <v>112</v>
-      </c>
-      <c r="P21">
+      <c r="P21" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q21">
         <v>-0.1101837620501105</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>0.0919228924848931</v>
       </c>
-      <c r="R21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="S21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
         <v>51</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>52</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.5201170436838566</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.5374321662622487</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-0.01731512257839207</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-0.1164926751154171</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.08380091829685227</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.7464</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.1949057415254287</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>1.374108209799784</v>
       </c>
-      <c r="M22" t="s">
-        <v>72</v>
-      </c>
-      <c r="N22">
+      <c r="N22" t="s">
+        <v>73</v>
+      </c>
+      <c r="O22">
         <v>0.9228</v>
       </c>
-      <c r="O22" t="s">
-        <v>112</v>
-      </c>
-      <c r="P22">
+      <c r="P22" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q22">
         <v>-0.1396788216727526</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>0.107729520460603</v>
       </c>
-      <c r="R22" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -6131,323 +6436,341 @@
         <v>94</v>
       </c>
       <c r="C23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" t="s">
         <v>51</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>52</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.36</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.35</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.01000000000000001</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-0.08000000000000002</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.09500000000000003</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.8336</v>
       </c>
-      <c r="M23" t="s">
-        <v>73</v>
-      </c>
-      <c r="N23">
+      <c r="N23" t="s">
+        <v>74</v>
+      </c>
+      <c r="O23">
         <v>0.8766</v>
       </c>
-      <c r="O23" t="s">
-        <v>112</v>
-      </c>
-      <c r="P23">
+      <c r="P23" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q23">
         <v>-0.09734129388236519</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>0.1173412938823652</v>
       </c>
-      <c r="R23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
         <v>51</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>52</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.5238220251826913</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.5410617974988647</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-0.01723977231617346</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>-0.117765501818481</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0.08218194600946505</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>0.751</v>
       </c>
-      <c r="M24" t="s">
-        <v>74</v>
-      </c>
-      <c r="N24">
+      <c r="N24" t="s">
+        <v>75</v>
+      </c>
+      <c r="O24">
         <v>0.9198</v>
       </c>
-      <c r="O24" t="s">
-        <v>112</v>
-      </c>
-      <c r="P24">
+      <c r="P24" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q24">
         <v>-0.1403678540165528</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>0.1052342909195122</v>
       </c>
-      <c r="R24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
         <v>51</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>52</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.7101449275362319</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>-0.0434782608695653</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>-0.1486789027833803</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0.05714285714285714</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>0.4104456923623511</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>-0.01013513513513513</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>1.568181818181818</v>
       </c>
-      <c r="M25" t="s">
-        <v>75</v>
-      </c>
-      <c r="N25">
+      <c r="N25" t="s">
+        <v>76</v>
+      </c>
+      <c r="O25">
         <v>0.8208913847247021</v>
       </c>
-      <c r="O25" t="s">
-        <v>113</v>
-      </c>
-      <c r="P25">
+      <c r="P25" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q25">
         <v>-0.1741545893719806</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>0.08108108108108114</v>
       </c>
-      <c r="R25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" t="s">
         <v>51</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>53</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.01043478260869565</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.06304347826086956</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>-0.05260869565217391</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>-0.1879810138775782</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>0.05830076237802242</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>0.3848</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>-0.03098345436095269</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>1.568181818181818</v>
       </c>
-      <c r="M26" t="s">
-        <v>72</v>
-      </c>
-      <c r="N26">
+      <c r="N26" t="s">
+        <v>73</v>
+      </c>
+      <c r="O26">
         <v>0.6546</v>
       </c>
-      <c r="O26" t="s">
-        <v>112</v>
-      </c>
-      <c r="P26">
+      <c r="P26" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q26">
         <v>-0.2000900155857261</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>0.09487262428137828</v>
       </c>
-      <c r="R26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="S26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
         <v>51</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>53</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.4165217391304348</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.4534782608695653</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>-0.0369565217391305</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>-0.1201436004796208</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>0.05199748898995496</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>0.39</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>-0.2695103572946947</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>1.568181818181818</v>
       </c>
-      <c r="M27" t="s">
-        <v>72</v>
-      </c>
-      <c r="N27">
+      <c r="N27" t="s">
+        <v>73</v>
+      </c>
+      <c r="O27">
         <v>0.6682</v>
       </c>
-      <c r="O27" t="s">
-        <v>112</v>
-      </c>
-      <c r="P27">
+      <c r="P27" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q27">
         <v>-0.1410315331593855</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>0.06711848968112478</v>
       </c>
-      <c r="R27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="S27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
         <v>51</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>53</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.5201170436838566</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.5544640969283843</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>-0.03434705324452769</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>-0.1272371763235338</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>0.06288154246470519</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>0.5024</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>-0.1848791046335549</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>1.568181818181818</v>
       </c>
-      <c r="M28" t="s">
-        <v>72</v>
-      </c>
-      <c r="N28">
+      <c r="N28" t="s">
+        <v>73</v>
+      </c>
+      <c r="O28">
         <v>0.7744</v>
       </c>
-      <c r="O28" t="s">
-        <v>112</v>
-      </c>
-      <c r="P28">
+      <c r="P28" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q28">
         <v>-0.144290130626136</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>0.08263711906375129</v>
       </c>
-      <c r="R28" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="S28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -6455,323 +6778,341 @@
         <v>94</v>
       </c>
       <c r="C29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" t="s">
         <v>51</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>53</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.36</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.4</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>-0.04000000000000004</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>-0.145</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>0.06999999999999995</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>0.5732</v>
       </c>
-      <c r="M29" t="s">
-        <v>73</v>
-      </c>
-      <c r="N29">
+      <c r="N29" t="s">
+        <v>74</v>
+      </c>
+      <c r="O29">
         <v>0.7028</v>
       </c>
-      <c r="O29" t="s">
-        <v>112</v>
-      </c>
-      <c r="P29">
+      <c r="P29" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q29">
         <v>-0.1700413668805986</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>0.09004136688059849</v>
       </c>
-      <c r="R29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="S29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>53</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.5238220251826913</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.5549040837833944</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>-0.03108205860070312</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>-0.1262655503625984</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>0.06957054598927924</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>0.5556</v>
       </c>
-      <c r="M30" t="s">
-        <v>74</v>
-      </c>
-      <c r="N30">
+      <c r="N30" t="s">
+        <v>75</v>
+      </c>
+      <c r="O30">
         <v>0.8274</v>
       </c>
-      <c r="O30" t="s">
-        <v>112</v>
-      </c>
-      <c r="P30">
+      <c r="P30" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q30">
         <v>-0.1469898117459688</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>0.08947643166486603</v>
       </c>
-      <c r="R30" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="S30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
         <v>51</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>53</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.6521739130434783</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.01449275362318836</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>-0.1475963668586618</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>0.1803392531876139</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>0.8633641527524397</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>0.08860617399438728</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>1.473567895472554</v>
       </c>
-      <c r="M31" t="s">
-        <v>75</v>
-      </c>
-      <c r="N31">
+      <c r="N31" t="s">
+        <v>76</v>
+      </c>
+      <c r="O31">
         <v>0.8633641527524397</v>
       </c>
-      <c r="O31" t="s">
-        <v>113</v>
-      </c>
-      <c r="P31">
+      <c r="P31" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q31">
         <v>-0.1818181818181818</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>0.2205882352941176</v>
       </c>
-      <c r="R31" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="S31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" t="s">
         <v>52</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>53</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.01811594202898551</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.06304347826086956</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>-0.04492753623188404</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>-0.1754659154641391</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>0.08188536834779539</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>0.4786</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>-0.04383859438246455</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>1.568181818181818</v>
       </c>
-      <c r="M32" t="s">
-        <v>72</v>
-      </c>
-      <c r="N32">
+      <c r="N32" t="s">
+        <v>73</v>
+      </c>
+      <c r="O32">
         <v>0.7151999999999999</v>
       </c>
-      <c r="O32" t="s">
-        <v>112</v>
-      </c>
-      <c r="P32">
+      <c r="P32" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q32">
         <v>-0.2027351339597176</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>0.1128800614959495</v>
       </c>
-      <c r="R32" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="S32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" t="s">
         <v>52</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>53</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.4256521739130435</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.4534782608695653</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>-0.02782608695652178</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>-0.1214282966917444</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>0.07867450219518883</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>0.5806</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>-0.03481933654805834</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>1.568181818181818</v>
       </c>
-      <c r="M33" t="s">
-        <v>72</v>
-      </c>
-      <c r="N33">
+      <c r="N33" t="s">
+        <v>73</v>
+      </c>
+      <c r="O33">
         <v>0.7912</v>
       </c>
-      <c r="O33" t="s">
-        <v>112</v>
-      </c>
-      <c r="P33">
+      <c r="P33" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q33">
         <v>-0.1503432645023226</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>0.09469109058927928</v>
       </c>
-      <c r="R33" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="S33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
         <v>52</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>53</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.5374321662622487</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.5544640969283843</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>-0.01703193066613562</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>-0.1356648710020678</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0.100814865669678</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>0.8066</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>-0.03807315394614937</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>1.568181818181818</v>
       </c>
-      <c r="M34" t="s">
-        <v>72</v>
-      </c>
-      <c r="N34">
+      <c r="N34" t="s">
+        <v>73</v>
+      </c>
+      <c r="O34">
         <v>0.9228</v>
       </c>
-      <c r="O34" t="s">
-        <v>112</v>
-      </c>
-      <c r="P34">
+      <c r="P34" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q34">
         <v>-0.1614748457486424</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>0.1308031113881423</v>
       </c>
-      <c r="R34" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="S34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -6779,323 +7120,341 @@
         <v>94</v>
       </c>
       <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" t="s">
         <v>52</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>53</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.35</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.4</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>-0.05000000000000004</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>-0.17</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>0.06</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>0.4592</v>
       </c>
-      <c r="M35" t="s">
-        <v>73</v>
-      </c>
-      <c r="N35">
+      <c r="N35" t="s">
+        <v>74</v>
+      </c>
+      <c r="O35">
         <v>0.6756</v>
       </c>
-      <c r="O35" t="s">
-        <v>112</v>
-      </c>
-      <c r="P35">
+      <c r="P35" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q35">
         <v>-0.1850000000000001</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>0.08500000000000002</v>
       </c>
-      <c r="R35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="S35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
         <v>52</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>53</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.5410617974988647</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.5549040837833944</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-0.01384228628452966</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-0.1354366941567308</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>0.1085662294439589</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>0.8346</v>
       </c>
-      <c r="M36" t="s">
-        <v>74</v>
-      </c>
-      <c r="N36">
+      <c r="N36" t="s">
+        <v>75</v>
+      </c>
+      <c r="O36">
         <v>0.9198</v>
       </c>
-      <c r="O36" t="s">
-        <v>112</v>
-      </c>
-      <c r="P36">
+      <c r="P36" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q36">
         <v>-0.1629424849920504</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>0.1368814188906857</v>
       </c>
-      <c r="R36" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="S36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
         <v>52</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>53</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.7101449275362319</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.6521739130434783</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>0.05797101449275366</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>-0.07142857142857142</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>0.1940298507462687</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>0.3988546137823287</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>-0.01065246338215713</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>1.568181818181818</v>
       </c>
-      <c r="M37" t="s">
-        <v>75</v>
-      </c>
-      <c r="N37">
+      <c r="N37" t="s">
+        <v>76</v>
+      </c>
+      <c r="O37">
         <v>0.7977092275646573</v>
       </c>
-      <c r="O37" t="s">
-        <v>113</v>
-      </c>
-      <c r="P37">
+      <c r="P37" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q37">
         <v>-0.1050316598824059</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>0.2277272727272732</v>
       </c>
-      <c r="R37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="S37" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" t="s">
         <v>51</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>52</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>0.01693277310924369</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.01974789915966386</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>-0.002815126050420166</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>-0.05748818465674033</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>0.05012159164749841</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>0.9176</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>0.1943278172079755</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>1.359032548719953</v>
       </c>
-      <c r="M38" t="s">
-        <v>72</v>
-      </c>
-      <c r="N38">
+      <c r="N38" t="s">
+        <v>73</v>
+      </c>
+      <c r="O38">
         <v>0.982</v>
       </c>
-      <c r="O38" t="s">
-        <v>112</v>
-      </c>
-      <c r="P38">
+      <c r="P38" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q38">
         <v>-0.06625616770219352</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>0.06062591560135315</v>
       </c>
-      <c r="R38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="S38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
         <v>51</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>52</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.3740756302521008</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.3876470588235295</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-0.01357142857142862</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>-0.06071090006005311</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>0.03126504210044222</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>0.5570000000000001</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>0.2103450236458073</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>1.345653477740814</v>
       </c>
-      <c r="M39" t="s">
-        <v>72</v>
-      </c>
-      <c r="N39">
+      <c r="N39" t="s">
+        <v>73</v>
+      </c>
+      <c r="O39">
         <v>0.5570000000000001</v>
       </c>
-      <c r="O39" t="s">
-        <v>112</v>
-      </c>
-      <c r="P39">
+      <c r="P39" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q39">
         <v>-0.06891405825293671</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>0.04177120111008013</v>
       </c>
-      <c r="R39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="S39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
         <v>51</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>52</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.4805271090386144</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.4957262730732819</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>-0.01519916403466753</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>-0.05959981574711692</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>0.02961214099715429</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>0.503</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>0.1856703660766267</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>1.366375422058099</v>
       </c>
-      <c r="M40" t="s">
-        <v>72</v>
-      </c>
-      <c r="N40">
+      <c r="N40" t="s">
+        <v>73</v>
+      </c>
+      <c r="O40">
         <v>0.503</v>
       </c>
-      <c r="O40" t="s">
-        <v>112</v>
-      </c>
-      <c r="P40">
+      <c r="P40" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q40">
         <v>-0.06924639598959506</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>0.04019670930361872</v>
       </c>
-      <c r="R40" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="S40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -7103,323 +7462,341 @@
         <v>94</v>
       </c>
       <c r="C41" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" t="s">
         <v>51</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>52</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.29</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.335</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>-0.04500000000000004</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>-0.105</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>0.03999999999999998</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>0.3164</v>
       </c>
-      <c r="M41" t="s">
-        <v>73</v>
-      </c>
-      <c r="N41">
+      <c r="N41" t="s">
+        <v>74</v>
+      </c>
+      <c r="O41">
         <v>0.3292</v>
       </c>
-      <c r="O41" t="s">
-        <v>112</v>
-      </c>
-      <c r="P41">
+      <c r="P41" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q41">
         <v>-0.131897207526139</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>0.04189720752613892</v>
       </c>
-      <c r="R41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="S41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" t="s">
         <v>51</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>52</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.4812407527715649</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.4963766811552734</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>-0.01513592838370859</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>-0.05940962551562724</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>0.02955483342924571</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>0.5008</v>
       </c>
-      <c r="M42" t="s">
-        <v>74</v>
-      </c>
-      <c r="N42">
+      <c r="N42" t="s">
+        <v>75</v>
+      </c>
+      <c r="O42">
         <v>0.5008</v>
       </c>
-      <c r="O42" t="s">
-        <v>112</v>
-      </c>
-      <c r="P42">
+      <c r="P42" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q42">
         <v>-0.06892480197736342</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>0.04023956149928003</v>
       </c>
-      <c r="R42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="S42" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" t="s">
         <v>51</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>52</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0.7394957983193278</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>0.6764705882352942</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>0.06302521008403361</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>-0.008298755186721992</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>0.1333333333333333</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>0.0785432549942764</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>0.06937498713753575</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>1.473305902152329</v>
       </c>
-      <c r="M43" t="s">
-        <v>75</v>
-      </c>
-      <c r="N43">
+      <c r="N43" t="s">
+        <v>76</v>
+      </c>
+      <c r="O43">
         <v>0.1570865099885528</v>
       </c>
-      <c r="O43" t="s">
-        <v>113</v>
-      </c>
-      <c r="P43">
+      <c r="P43" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q43">
         <v>-0.0212179949513163</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>0.1483633705869293</v>
       </c>
-      <c r="R43" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="S43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" t="s">
         <v>51</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>53</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.01693277310924369</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.01130252100840337</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>0.005630252100840326</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>-0.06081467861304428</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>0.07283379687072547</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>0.862</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>0.2479815712178917</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>1.315229181497365</v>
       </c>
-      <c r="M44" t="s">
-        <v>72</v>
-      </c>
-      <c r="N44">
+      <c r="N44" t="s">
+        <v>73</v>
+      </c>
+      <c r="O44">
         <v>0.982</v>
       </c>
-      <c r="O44" t="s">
-        <v>112</v>
-      </c>
-      <c r="P44">
+      <c r="P44" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q44">
         <v>-0.0744154556769744</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>0.08567595987865505</v>
       </c>
-      <c r="R44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="S44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" t="s">
         <v>51</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>53</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.3740756302521008</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.4584453781512605</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>-0.08436974789915969</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>-0.1398838651624345</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>-0.0295327372730704</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>0.0034</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>0.2617227998154008</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>1.304461201119753</v>
       </c>
-      <c r="M45" t="s">
-        <v>72</v>
-      </c>
-      <c r="N45">
+      <c r="N45" t="s">
+        <v>73</v>
+      </c>
+      <c r="O45">
         <v>0.009599999999999999</v>
       </c>
-      <c r="O45" t="s">
-        <v>112</v>
-      </c>
-      <c r="P45">
+      <c r="P45" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q45">
         <v>-0.1507495494343032</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>-0.01798994636401634</v>
       </c>
-      <c r="R45" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="S45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" t="s">
         <v>51</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>53</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.4805271090386144</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.5806744123080022</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>-0.1001473032693878</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>-0.1606451278002748</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>-0.03734422411782519</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>0.0032</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>0.2003745902317424</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>1.353950574887211</v>
       </c>
-      <c r="M46" t="s">
-        <v>72</v>
-      </c>
-      <c r="N46">
+      <c r="N46" t="s">
+        <v>73</v>
+      </c>
+      <c r="O46">
         <v>0.0058</v>
       </c>
-      <c r="O46" t="s">
-        <v>112</v>
-      </c>
-      <c r="P46">
+      <c r="P46" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q46">
         <v>-0.1735680846859624</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>-0.02302037088749732</v>
       </c>
-      <c r="R46" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="S46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -7427,323 +7804,341 @@
         <v>94</v>
       </c>
       <c r="C47" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" t="s">
         <v>51</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>53</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.29</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.37</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>-0.08000000000000002</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>-0.16</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>0</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>0.0716</v>
       </c>
-      <c r="M47" t="s">
-        <v>73</v>
-      </c>
-      <c r="N47">
+      <c r="N47" t="s">
+        <v>74</v>
+      </c>
+      <c r="O47">
         <v>0.125</v>
       </c>
-      <c r="O47" t="s">
-        <v>112</v>
-      </c>
-      <c r="P47">
+      <c r="P47" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q47">
         <v>-0.1748543278868911</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>0.01485432788689105</v>
       </c>
-      <c r="R47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="S47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" t="s">
         <v>51</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>53</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.4812407527715649</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.581787933214607</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>-0.1005471804430421</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>-0.1598467389143226</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>-0.03791708938899847</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>0.0042</v>
       </c>
-      <c r="M48" t="s">
-        <v>74</v>
-      </c>
-      <c r="N48">
+      <c r="N48" t="s">
+        <v>75</v>
+      </c>
+      <c r="O48">
         <v>0.0114</v>
       </c>
-      <c r="O48" t="s">
-        <v>112</v>
-      </c>
-      <c r="P48">
+      <c r="P48" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q48">
         <v>-0.173472335352231</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>-0.02353042056685119</v>
       </c>
-      <c r="R48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="S48" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" t="s">
         <v>51</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>53</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.7394957983193278</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>0.6386554621848739</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>0.1008403361344539</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>0.02574557059535602</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>0.1769547325102881</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>0.01051393361055575</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>0.2828519996869374</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>1.288243537854977</v>
       </c>
-      <c r="M49" t="s">
-        <v>75</v>
-      </c>
-      <c r="N49">
+      <c r="N49" t="s">
+        <v>76</v>
+      </c>
+      <c r="O49">
         <v>0.03154180083166726</v>
       </c>
-      <c r="O49" t="s">
-        <v>113</v>
-      </c>
-      <c r="P49">
+      <c r="P49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q49">
         <v>0.008498016588532281</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>0.1965811965811965</v>
       </c>
-      <c r="R49" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18">
+      <c r="S49" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" t="s">
         <v>52</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>53</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.01974789915966386</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>0.01130252100840337</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>0.008445378151260492</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>-0.06093731332680365</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>0.07706069689774481</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>0.8086</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>0.1799810231676754</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>1.371244234613271</v>
       </c>
-      <c r="M50" t="s">
-        <v>72</v>
-      </c>
-      <c r="N50">
+      <c r="N50" t="s">
+        <v>73</v>
+      </c>
+      <c r="O50">
         <v>0.9704</v>
       </c>
-      <c r="O50" t="s">
-        <v>112</v>
-      </c>
-      <c r="P50">
+      <c r="P50" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q50">
         <v>-0.07491254037785042</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>0.09180329668037143</v>
       </c>
-      <c r="R50" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="S50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" t="s">
         <v>52</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>53</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.3876470588235295</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>0.4584453781512605</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>-0.07079831932773106</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>-0.1273640479129107</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>-0.0154243638359112</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>0.0158</v>
       </c>
-      <c r="K51">
+      <c r="L51">
         <v>0.2066823974584756</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>1.348689562693561</v>
       </c>
-      <c r="M51" t="s">
-        <v>72</v>
-      </c>
-      <c r="N51">
+      <c r="N51" t="s">
+        <v>73</v>
+      </c>
+      <c r="O51">
         <v>0.0308</v>
       </c>
-      <c r="O51" t="s">
-        <v>112</v>
-      </c>
-      <c r="P51">
+      <c r="P51" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q51">
         <v>-0.1394101766616208</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>-0.002186461993842218</v>
       </c>
-      <c r="R51" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" t="s">
         <v>52</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>53</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.4957262730732819</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>0.5806744123080022</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>-0.08494813923472028</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>-0.1446335592384758</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>-0.02545425540213038</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>0.0092</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>0.09316285966893136</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>1.450093471617067</v>
       </c>
-      <c r="M52" t="s">
-        <v>72</v>
-      </c>
-      <c r="N52">
+      <c r="N52" t="s">
+        <v>73</v>
+      </c>
+      <c r="O52">
         <v>0.0178</v>
       </c>
-      <c r="O52" t="s">
-        <v>112</v>
-      </c>
-      <c r="P52">
+      <c r="P52" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q52">
         <v>-0.157354026556972</v>
       </c>
-      <c r="Q52">
+      <c r="R52">
         <v>-0.01043630456801225</v>
       </c>
-      <c r="R52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -7751,323 +8146,341 @@
         <v>94</v>
       </c>
       <c r="C53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" t="s">
         <v>52</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>53</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.335</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0.37</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>-0.03499999999999998</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>-0.13</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>0.04999999999999999</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>0.454</v>
       </c>
-      <c r="M53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N53">
+      <c r="N53" t="s">
+        <v>74</v>
+      </c>
+      <c r="O53">
         <v>0.4868</v>
       </c>
-      <c r="O53" t="s">
-        <v>112</v>
-      </c>
-      <c r="P53">
+      <c r="P53" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q53">
         <v>-0.145</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>0.07500000000000001</v>
       </c>
-      <c r="R53" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="S53" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54" t="s">
         <v>52</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>53</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.4963766811552734</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>0.581787933214607</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>-0.08541125205933353</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>-0.1444532979412127</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>-0.0259623222200178</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>0.0078</v>
       </c>
-      <c r="M54" t="s">
-        <v>74</v>
-      </c>
-      <c r="N54">
+      <c r="N54" t="s">
+        <v>75</v>
+      </c>
+      <c r="O54">
         <v>0.0204</v>
       </c>
-      <c r="O54" t="s">
-        <v>112</v>
-      </c>
-      <c r="P54">
+      <c r="P54" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q54">
         <v>-0.1571408854458069</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>-0.009901327367602573</v>
       </c>
-      <c r="R54" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="S54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" t="s">
         <v>52</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>53</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.6764705882352942</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>0.6386554621848739</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>0.03781512605042026</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>-0.04166666666666666</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>0.1174456345342423</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>0.3611297063274773</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>0.23582236229011</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>1.324906792740472</v>
       </c>
-      <c r="M55" t="s">
-        <v>75</v>
-      </c>
-      <c r="N55">
+      <c r="N55" t="s">
+        <v>76</v>
+      </c>
+      <c r="O55">
         <v>0.3611297063274773</v>
       </c>
-      <c r="O55" t="s">
-        <v>113</v>
-      </c>
-      <c r="P55">
+      <c r="P55" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q55">
         <v>-0.0595744680851064</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>0.1346938775510204</v>
       </c>
-      <c r="R55" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="S55" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56" t="s">
         <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" t="s">
         <v>51</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>52</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>0.03606060606060607</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>0.05505050505050505</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>-0.01898989898989898</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>-0.08862496046271545</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>0.05388728593976482</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>0.6018</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>-0.2904474668586193</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>1.546875</v>
       </c>
-      <c r="M56" t="s">
-        <v>72</v>
-      </c>
-      <c r="N56">
+      <c r="N56" t="s">
+        <v>73</v>
+      </c>
+      <c r="O56">
         <v>0.6018</v>
       </c>
-      <c r="O56" t="s">
-        <v>112</v>
-      </c>
-      <c r="P56">
+      <c r="P56" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q56">
         <v>-0.1041717788624654</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>0.06619198088266737</v>
       </c>
-      <c r="R56" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="S56" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57" t="s">
         <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" t="s">
         <v>51</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>52</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>0.4552525252525252</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>0.4681818181818182</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>-0.01292929292929296</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>-0.07435904196308235</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>0.055124609713654</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>0.6848</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>-0.106425305850861</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>1.546875</v>
       </c>
-      <c r="M57" t="s">
-        <v>72</v>
-      </c>
-      <c r="N57">
+      <c r="N57" t="s">
+        <v>73</v>
+      </c>
+      <c r="O57">
         <v>0.6848</v>
       </c>
-      <c r="O57" t="s">
-        <v>112</v>
-      </c>
-      <c r="P57">
+      <c r="P57" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q57">
         <v>-0.09169388423036738</v>
       </c>
-      <c r="Q57">
+      <c r="R57">
         <v>0.06583529837178102</v>
       </c>
-      <c r="R57" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="S57" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58" t="s">
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" t="s">
         <v>51</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>52</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>0.543478322353971</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>0.559177787452075</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>-0.01569946509810405</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>-0.08072115640039265</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>0.05111977716054127</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>0.6614</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>-0.1555075394087764</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>1.546875</v>
       </c>
-      <c r="M58" t="s">
-        <v>72</v>
-      </c>
-      <c r="N58">
+      <c r="N58" t="s">
+        <v>73</v>
+      </c>
+      <c r="O58">
         <v>0.6614</v>
       </c>
-      <c r="O58" t="s">
-        <v>112</v>
-      </c>
-      <c r="P58">
+      <c r="P58" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q58">
         <v>-0.09287133053075676</v>
       </c>
-      <c r="Q58">
+      <c r="R58">
         <v>0.06492253544918662</v>
       </c>
-      <c r="R58" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="S58" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
         <v>50</v>
       </c>
@@ -8075,323 +8488,341 @@
         <v>94</v>
       </c>
       <c r="C59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" t="s">
         <v>51</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>52</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>0.45</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>0.44</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>0.01000000000000001</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>-0.11</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>0.11</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>0.9892</v>
       </c>
-      <c r="M59" t="s">
-        <v>73</v>
-      </c>
-      <c r="N59">
+      <c r="N59" t="s">
+        <v>74</v>
+      </c>
+      <c r="O59">
         <v>0.9892</v>
       </c>
-      <c r="O59" t="s">
-        <v>112</v>
-      </c>
-      <c r="P59">
+      <c r="P59" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q59">
         <v>-0.114656049457789</v>
       </c>
-      <c r="Q59">
+      <c r="R59">
         <v>0.134656049457789</v>
       </c>
-      <c r="R59" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="S59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19">
       <c r="A60" t="s">
         <v>50</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
+        <v>99</v>
+      </c>
+      <c r="D60" t="s">
         <v>51</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>52</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>0.5450403807953941</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>0.5592932379303726</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>-0.01425285713497848</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>-0.08059016955817802</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>0.05341654811530116</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>0.6748</v>
       </c>
-      <c r="M60" t="s">
-        <v>74</v>
-      </c>
-      <c r="N60">
+      <c r="N60" t="s">
+        <v>75</v>
+      </c>
+      <c r="O60">
         <v>0.6748</v>
       </c>
-      <c r="O60" t="s">
-        <v>112</v>
-      </c>
-      <c r="P60">
+      <c r="P60" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q60">
         <v>-0.09379365909437119</v>
       </c>
-      <c r="Q60">
+      <c r="R60">
         <v>0.06854289563696495</v>
       </c>
-      <c r="R60" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="S60" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61" t="s">
         <v>50</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" t="s">
         <v>51</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>52</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>0.5959595959595959</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>0.5757575757575758</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>0.02020202020202011</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>-0.09900990099009901</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>0.1320754716981132</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>0.7329150910757301</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>-0.07978330658105939</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>1.546875</v>
       </c>
-      <c r="M61" t="s">
-        <v>75</v>
-      </c>
-      <c r="N61">
+      <c r="N61" t="s">
+        <v>76</v>
+      </c>
+      <c r="O61">
         <v>0.7329150910757301</v>
       </c>
-      <c r="O61" t="s">
-        <v>113</v>
-      </c>
-      <c r="P61">
+      <c r="P61" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q61">
         <v>-0.1254247572815532</v>
       </c>
-      <c r="Q61">
+      <c r="R61">
         <v>0.1601320754716982</v>
       </c>
-      <c r="R61" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18">
+      <c r="S61" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
         <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" t="s">
         <v>51</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>53</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>0.03606060606060607</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>0.1149494949494949</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>-0.07888888888888887</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>-0.1770903863284953</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>0.01515153893145468</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>0.1058</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>0.02059518934996596</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>1.52467233255561</v>
       </c>
-      <c r="M62" t="s">
-        <v>72</v>
-      </c>
-      <c r="N62">
+      <c r="N62" t="s">
+        <v>73</v>
+      </c>
+      <c r="O62">
         <v>0.2266</v>
       </c>
-      <c r="O62" t="s">
-        <v>112</v>
-      </c>
-      <c r="P62">
+      <c r="P62" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q62">
         <v>-0.1930728623380932</v>
       </c>
-      <c r="Q62">
+      <c r="R62">
         <v>0.03529508456031522</v>
       </c>
-      <c r="R62" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18">
+      <c r="S62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
       <c r="A63" t="s">
         <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" t="s">
         <v>51</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>53</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>0.4552525252525252</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>0.5197979797979798</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>-0.06454545454545457</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>-0.1304029636920622</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>-0.005277721363423381</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>0.045</v>
       </c>
-      <c r="K63">
+      <c r="L63">
         <v>-0.1754230967541944</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>1.546875</v>
       </c>
-      <c r="M63" t="s">
-        <v>72</v>
-      </c>
-      <c r="N63">
+      <c r="N63" t="s">
+        <v>73</v>
+      </c>
+      <c r="O63">
         <v>0.119</v>
       </c>
-      <c r="O63" t="s">
-        <v>112</v>
-      </c>
-      <c r="P63">
+      <c r="P63" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q63">
         <v>-0.1428151845382822</v>
       </c>
-      <c r="Q63">
+      <c r="R63">
         <v>0.01372427544737288</v>
       </c>
-      <c r="R63" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18">
+      <c r="S63" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64" t="s">
         <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" t="s">
         <v>51</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>53</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>0.543478322353971</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>0.6253112356372157</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>-0.08183291328324471</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>-0.1462367376518515</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>-0.01656233111272169</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>0.0324</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>-0.2623026064131282</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>1.546875</v>
       </c>
-      <c r="M64" t="s">
-        <v>72</v>
-      </c>
-      <c r="N64">
+      <c r="N64" t="s">
+        <v>73</v>
+      </c>
+      <c r="O64">
         <v>0.0764</v>
       </c>
-      <c r="O64" t="s">
-        <v>112</v>
-      </c>
-      <c r="P64">
+      <c r="P64" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q64">
         <v>-0.1608339457403495</v>
       </c>
-      <c r="Q64">
+      <c r="R64">
         <v>-0.004960680388902138</v>
       </c>
-      <c r="R64" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18">
+      <c r="S64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -8399,323 +8830,341 @@
         <v>94</v>
       </c>
       <c r="C65" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" t="s">
         <v>51</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>53</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>0.45</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>0.49</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>-0.03999999999999998</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>-0.12</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>0.04999999999999999</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>0.6532</v>
       </c>
-      <c r="M65" t="s">
-        <v>73</v>
-      </c>
-      <c r="N65">
+      <c r="N65" t="s">
+        <v>74</v>
+      </c>
+      <c r="O65">
         <v>0.7156</v>
       </c>
-      <c r="O65" t="s">
-        <v>112</v>
-      </c>
-      <c r="P65">
+      <c r="P65" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q65">
         <v>-0.14</v>
       </c>
-      <c r="Q65">
+      <c r="R65">
         <v>0.06000000000000004</v>
       </c>
-      <c r="R65" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18">
+      <c r="S65" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" t="s">
         <v>50</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66" t="s">
         <v>51</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>53</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>0.5450403807953941</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>0.6177830240223103</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>-0.07274264322691626</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>-0.1326539191798262</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>-0.01153379621125429</v>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>0.029</v>
       </c>
-      <c r="M66" t="s">
-        <v>74</v>
-      </c>
-      <c r="N66">
+      <c r="N66" t="s">
+        <v>75</v>
+      </c>
+      <c r="O66">
         <v>0.0992</v>
       </c>
-      <c r="O66" t="s">
-        <v>112</v>
-      </c>
-      <c r="P66">
+      <c r="P66" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q66">
         <v>-0.1432527526244144</v>
       </c>
-      <c r="Q66">
+      <c r="R66">
         <v>0.001523501976089357</v>
       </c>
-      <c r="R66" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18">
+      <c r="S66" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" t="s">
         <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C67" t="s">
+        <v>100</v>
+      </c>
+      <c r="D67" t="s">
         <v>51</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>53</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>0.5959595959595959</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>0.5252525252525253</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>0.07070707070707061</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>-0.0396039603960396</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>0.1747572815533981</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>0.2080477461314518</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>-0.1782954165272666</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>1.546875</v>
       </c>
-      <c r="M67" t="s">
-        <v>75</v>
-      </c>
-      <c r="N67">
+      <c r="N67" t="s">
+        <v>76</v>
+      </c>
+      <c r="O67">
         <v>0.6241432383943554</v>
       </c>
-      <c r="O67" t="s">
-        <v>113</v>
-      </c>
-      <c r="P67">
+      <c r="P67" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q67">
         <v>-0.06122448979591832</v>
       </c>
-      <c r="Q67">
+      <c r="R67">
         <v>0.2</v>
       </c>
-      <c r="R67" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18">
+      <c r="S67" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" t="s">
         <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" t="s">
         <v>52</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>53</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>0.05505050505050505</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>0.1149494949494949</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>-0.05989898989898989</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>-0.1734529329899067</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>0.04550799786446531</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>0.2758</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>0.3926960711657209</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>1.210705736991787</v>
       </c>
-      <c r="M68" t="s">
-        <v>72</v>
-      </c>
-      <c r="N68">
+      <c r="N68" t="s">
+        <v>73</v>
+      </c>
+      <c r="O68">
         <v>0.4524</v>
       </c>
-      <c r="O68" t="s">
-        <v>112</v>
-      </c>
-      <c r="P68">
+      <c r="P68" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q68">
         <v>-0.1906136501021066</v>
       </c>
-      <c r="Q68">
+      <c r="R68">
         <v>0.07081567030412667</v>
       </c>
-      <c r="R68" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18">
+      <c r="S68" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
       <c r="A69" t="s">
         <v>50</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69" t="s">
         <v>52</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>53</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>0.4681818181818182</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>0.5197979797979798</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>-0.05161616161616162</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>-0.1467751922665724</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>0.02086892772980065</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>0.224</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>0.2988823474395362</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>1.277004435911887</v>
       </c>
-      <c r="M69" t="s">
-        <v>72</v>
-      </c>
-      <c r="N69">
+      <c r="N69" t="s">
+        <v>73</v>
+      </c>
+      <c r="O69">
         <v>0.3428</v>
       </c>
-      <c r="O69" t="s">
-        <v>112</v>
-      </c>
-      <c r="P69">
+      <c r="P69" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q69">
         <v>-0.1526720041364751</v>
       </c>
-      <c r="Q69">
+      <c r="R69">
         <v>0.04943968090415207</v>
       </c>
-      <c r="R69" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18">
+      <c r="S69" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70" t="s">
         <v>50</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" t="s">
         <v>52</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>53</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>0.559177787452075</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>0.6253112356372157</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>-0.06613344818514066</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>-0.1528966205025178</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>0.01365989588905082</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>0.1566</v>
       </c>
-      <c r="K70">
+      <c r="L70">
         <v>0.2015912523625502</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>1.35389219565621</v>
       </c>
-      <c r="M70" t="s">
-        <v>72</v>
-      </c>
-      <c r="N70">
+      <c r="N70" t="s">
+        <v>73</v>
+      </c>
+      <c r="O70">
         <v>0.2464</v>
       </c>
-      <c r="O70" t="s">
-        <v>112</v>
-      </c>
-      <c r="P70">
+      <c r="P70" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q70">
         <v>-0.1757994104417805</v>
       </c>
-      <c r="Q70">
+      <c r="R70">
         <v>0.02953438105763693</v>
       </c>
-      <c r="R70" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18">
+      <c r="S70" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -8723,152 +9172,161 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" t="s">
         <v>52</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>53</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>0.44</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>0.49</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>-0.04999999999999999</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>-0.16</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>0.08500000000000002</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>0.6528</v>
       </c>
-      <c r="M71" t="s">
-        <v>73</v>
-      </c>
-      <c r="N71">
+      <c r="N71" t="s">
+        <v>74</v>
+      </c>
+      <c r="O71">
         <v>0.7156</v>
       </c>
-      <c r="O71" t="s">
-        <v>112</v>
-      </c>
-      <c r="P71">
+      <c r="P71" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q71">
         <v>-0.1935531761552672</v>
       </c>
-      <c r="Q71">
+      <c r="R71">
         <v>0.09355317615526718</v>
       </c>
-      <c r="R71" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18">
+      <c r="S71" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72" t="s">
         <v>50</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" t="s">
         <v>52</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>53</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>0.5592932379303726</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>0.6177830240223103</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>-0.05848978609193778</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>-0.1360691728962422</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>0.01505136763452953</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>0.148</v>
       </c>
-      <c r="M72" t="s">
-        <v>74</v>
-      </c>
-      <c r="N72">
+      <c r="N72" t="s">
+        <v>75</v>
+      </c>
+      <c r="O72">
         <v>0.2186</v>
       </c>
-      <c r="O72" t="s">
-        <v>112</v>
-      </c>
-      <c r="P72">
+      <c r="P72" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q72">
         <v>-0.1521339969166954</v>
       </c>
-      <c r="Q72">
+      <c r="R72">
         <v>0.03162738926570315</v>
       </c>
-      <c r="R72" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
+      <c r="S72" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73" t="s">
         <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" t="s">
         <v>52</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>53</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>0.5757575757575758</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>0.5252525252525253</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>0.0505050505050505</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>-0.0721930646672914</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>0.1739552553820179</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>0.4273643299212784</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>0.1555398671096345</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>1.393609099133894</v>
       </c>
-      <c r="M73" t="s">
-        <v>75</v>
-      </c>
-      <c r="N73">
+      <c r="N73" t="s">
+        <v>76</v>
+      </c>
+      <c r="O73">
         <v>0.7329150910757301</v>
       </c>
-      <c r="O73" t="s">
-        <v>113</v>
-      </c>
-      <c r="P73">
+      <c r="P73" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q73">
         <v>-0.09999999999999998</v>
       </c>
-      <c r="Q73">
+      <c r="R73">
         <v>0.2021276595744681</v>
       </c>
-      <c r="R73" t="s">
-        <v>115</v>
+      <c r="S73" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -8878,265 +9336,281 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="60.7109375" customWidth="1"/>
-    <col min="3" max="17" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="4" max="18" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I1" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="J1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <v>132</v>
+      </c>
+      <c r="R1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
         <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G2">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2">
         <v>406</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>250</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>156</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.624</v>
       </c>
-      <c r="K2" t="b">
+      <c r="L2" t="b">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>4999</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>42</v>
       </c>
-      <c r="N2" t="s">
-        <v>137</v>
-      </c>
       <c r="O2" t="s">
-        <v>138</v>
-      </c>
-      <c r="P2" t="b">
+        <v>141</v>
+      </c>
+      <c r="P2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G3">
+        <v>139</v>
+      </c>
+      <c r="F3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3">
         <v>69</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>44</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>25</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.5681818181818182</v>
       </c>
-      <c r="K3" t="b">
+      <c r="L3" t="b">
         <v>1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>4999</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
-        <v>137</v>
-      </c>
       <c r="O3" t="s">
-        <v>138</v>
-      </c>
-      <c r="P3" t="b">
+        <v>141</v>
+      </c>
+      <c r="P3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4">
+        <v>139</v>
+      </c>
+      <c r="F4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4">
         <v>238</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>154</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>84</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.5454545454545454</v>
       </c>
-      <c r="K4" t="b">
+      <c r="L4" t="b">
         <v>1</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>4999</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
-        <v>137</v>
-      </c>
       <c r="O4" t="s">
-        <v>138</v>
-      </c>
-      <c r="P4" t="b">
+        <v>141</v>
+      </c>
+      <c r="P4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q4" t="b">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5">
+        <v>139</v>
+      </c>
+      <c r="F5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5">
         <v>99</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>64</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>35</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.546875</v>
       </c>
-      <c r="K5" t="b">
+      <c r="L5" t="b">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>4999</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>42</v>
       </c>
-      <c r="N5" t="s">
-        <v>137</v>
-      </c>
       <c r="O5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P5" t="b">
+        <v>141</v>
+      </c>
+      <c r="P5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q5" t="b">
         <v>0</v>
       </c>
-      <c r="Q5" t="s">
-        <v>139</v>
+      <c r="R5" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_continuous_errors_results.xlsx
+++ b/examples/example_continuous_errors_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="139">
   <si>
     <t>Group</t>
   </si>
@@ -86,12 +86,6 @@
     <t>RMSE Diff 95% CI high</t>
   </si>
   <si>
-    <t>RMSE Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>RMSE Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Boot (RMSE) p</t>
   </si>
   <si>
@@ -128,12 +122,6 @@
     <t>SD Diff 95% CI high</t>
   </si>
   <si>
-    <t>SD Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>SD Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Morgan-Pitman (SD) p</t>
   </si>
   <si>
@@ -149,12 +137,6 @@
     <t>McNemar Diff 95% CI high</t>
   </si>
   <si>
-    <t>McNemar Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>McNemar Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>McNemar p</t>
   </si>
   <si>
@@ -194,22 +176,22 @@
     <t>Weighting of Eyes (mean-loss metrics)</t>
   </si>
   <si>
-    <t>Mean error Test</t>
-  </si>
-  <si>
-    <t>Mean absolute error Test</t>
-  </si>
-  <si>
-    <t>Root mean squared error Test</t>
-  </si>
-  <si>
-    <t>Median absolute error Test</t>
-  </si>
-  <si>
-    <t>SD of the error Test</t>
-  </si>
-  <si>
-    <t>Proportion within tolerance Test</t>
+    <t>Mean Error (MPE) Test</t>
+  </si>
+  <si>
+    <t>MAE Test</t>
+  </si>
+  <si>
+    <t>RMSE Test</t>
+  </si>
+  <si>
+    <t>MedAE Test</t>
+  </si>
+  <si>
+    <t>SD Test</t>
+  </si>
+  <si>
+    <t>Proportion Within Tolerance Test</t>
   </si>
   <si>
     <t>Tolerance (proportion within)</t>
@@ -257,10 +239,10 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean error, Mean absolute error, Root mean squared error, Median absolute error, SD of the error; Hommel: Proportion within tolerance</t>
-  </si>
-  <si>
-    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean error, Mean absolute error, Median absolute error; Bonferroni (percentile bootstrap): Root mean squared error, SD of the error, Proportion within tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean Error (MPE), MAE, RMSE, MedAE, SD; Hommel: Proportion Within Tolerance</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group, for the MPE, MAE and MedAE only: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). The RMSE, SD and the proportion within tolerance have no adjusted interval: their adjusted p-values (Romano-Wolf from a different statistic, or Hommel) have no matching interval, so their CIs are unadjusted. fwer_method='bonferroni' gives Bonferroni p-values with matching intervals for every metric</t>
   </si>
   <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
@@ -377,7 +359,10 @@
     <t>Romano-Wolf simultaneous (max-|t|)</t>
   </si>
   <si>
-    <t>Bonferroni (percentile bootstrap)</t>
+    <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
+  </si>
+  <si>
+    <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
   </si>
   <si>
     <t>definition</t>
@@ -781,24 +766,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="12" width="15.7109375" customWidth="1"/>
     <col min="13" max="17" width="22.7109375" customWidth="1"/>
     <col min="18" max="19" width="15.7109375" customWidth="1"/>
-    <col min="20" max="24" width="22.7109375" customWidth="1"/>
-    <col min="25" max="26" width="15.7109375" customWidth="1"/>
-    <col min="27" max="31" width="22.7109375" customWidth="1"/>
-    <col min="32" max="33" width="15.7109375" customWidth="1"/>
-    <col min="34" max="38" width="22.7109375" customWidth="1"/>
-    <col min="39" max="40" width="15.7109375" customWidth="1"/>
-    <col min="41" max="45" width="22.7109375" customWidth="1"/>
-    <col min="46" max="47" width="15.7109375" customWidth="1"/>
+    <col min="20" max="22" width="22.7109375" customWidth="1"/>
+    <col min="23" max="24" width="15.7109375" customWidth="1"/>
+    <col min="25" max="29" width="22.7109375" customWidth="1"/>
+    <col min="30" max="31" width="15.7109375" customWidth="1"/>
+    <col min="32" max="34" width="22.7109375" customWidth="1"/>
+    <col min="35" max="36" width="15.7109375" customWidth="1"/>
+    <col min="37" max="39" width="22.7109375" customWidth="1"/>
+    <col min="40" max="41" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -922,34 +907,16 @@
       <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+    </row>
+    <row r="2" spans="1:41">
+      <c r="A2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="B2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="C2" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
       </c>
       <c r="D2">
         <v>406</v>
@@ -1009,90 +976,72 @@
         <v>0.01787937336349218</v>
       </c>
       <c r="W2">
-        <v>-0.05856576544801699</v>
+        <v>0.3852</v>
       </c>
       <c r="X2">
-        <v>0.02781683152088923</v>
+        <v>0.3852</v>
       </c>
       <c r="Y2">
-        <v>0.3852</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="Z2">
-        <v>0.3852</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA2">
-        <v>-0.009999999999999953</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000001</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AC2">
-        <v>0.03999999999999998</v>
+        <v>0.06000000000000011</v>
       </c>
       <c r="AD2">
-        <v>-0.08000000000000002</v>
+        <v>0.6968</v>
       </c>
       <c r="AE2">
-        <v>0.06000000000000011</v>
+        <v>0.844</v>
       </c>
       <c r="AF2">
-        <v>0.6968</v>
+        <v>-0.01535687255151641</v>
       </c>
       <c r="AG2">
-        <v>0.844</v>
+        <v>-0.05064189418206674</v>
       </c>
       <c r="AH2">
-        <v>-0.01535687255151641</v>
+        <v>0.01876017330561083</v>
       </c>
       <c r="AI2">
-        <v>-0.05064189418206674</v>
+        <v>0.3894</v>
       </c>
       <c r="AJ2">
-        <v>0.01876017330561083</v>
+        <v>0.3894</v>
       </c>
       <c r="AK2">
-        <v>-0.05815433485882694</v>
+        <v>0.03448275862068961</v>
       </c>
       <c r="AL2">
-        <v>0.02825025172545625</v>
+        <v>-0.01805205348027686</v>
       </c>
       <c r="AM2">
-        <v>0.3894</v>
+        <v>0.08780487804878048</v>
       </c>
       <c r="AN2">
-        <v>0.3894</v>
+        <v>0.204560421762222</v>
       </c>
       <c r="AO2">
-        <v>0.03448275862068961</v>
-      </c>
-      <c r="AP2">
-        <v>-0.01805205348027686</v>
-      </c>
-      <c r="AQ2">
-        <v>0.08780487804878048</v>
-      </c>
-      <c r="AR2">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="AS2">
-        <v>0.09762516046213096</v>
-      </c>
-      <c r="AT2">
         <v>0.204560421762222</v>
       </c>
-      <c r="AU2">
-        <v>0.204560421762222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:47">
+    </row>
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
         <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
       </c>
       <c r="D3">
         <v>406</v>
@@ -1152,90 +1101,72 @@
         <v>-0.0419672383242247</v>
       </c>
       <c r="W3">
-        <v>-0.1343146850892963</v>
+        <v>0.0004</v>
       </c>
       <c r="X3">
-        <v>-0.03239054644227168</v>
+        <v>0.0008</v>
       </c>
       <c r="Y3">
-        <v>0.0004</v>
+        <v>-0.06</v>
       </c>
       <c r="Z3">
+        <v>-0.12</v>
+      </c>
+      <c r="AA3">
+        <v>-0.009999999999999953</v>
+      </c>
+      <c r="AB3">
+        <v>-0.1280741611297382</v>
+      </c>
+      <c r="AC3">
+        <v>0.008074161129738258</v>
+      </c>
+      <c r="AD3">
+        <v>0.0392</v>
+      </c>
+      <c r="AE3">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="AF3">
+        <v>-0.08300106659587148</v>
+      </c>
+      <c r="AG3">
+        <v>-0.124012759523577</v>
+      </c>
+      <c r="AH3">
+        <v>-0.04070333062114999</v>
+      </c>
+      <c r="AI3">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="AJ3">
         <v>0.0008</v>
       </c>
-      <c r="AA3">
-        <v>-0.06</v>
-      </c>
-      <c r="AB3">
-        <v>-0.12</v>
-      </c>
-      <c r="AC3">
-        <v>-0.009999999999999953</v>
-      </c>
-      <c r="AD3">
-        <v>-0.1280741611297382</v>
-      </c>
-      <c r="AE3">
-        <v>0.008074161129738258</v>
-      </c>
-      <c r="AF3">
-        <v>0.0392</v>
-      </c>
-      <c r="AG3">
-        <v>0.09859999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>-0.08300106659587148</v>
-      </c>
-      <c r="AI3">
-        <v>-0.124012759523577</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.04070333062114999</v>
-      </c>
       <c r="AK3">
-        <v>-0.1324121069898527</v>
+        <v>0.0788177339901478</v>
       </c>
       <c r="AL3">
-        <v>-0.03081160526701515</v>
+        <v>0.01979710286299567</v>
       </c>
       <c r="AM3">
-        <v>0.0005999999999999999</v>
+        <v>0.1380185633575464</v>
       </c>
       <c r="AN3">
-        <v>0.0008</v>
+        <v>0.009022063055144957</v>
       </c>
       <c r="AO3">
-        <v>0.0788177339901478</v>
-      </c>
-      <c r="AP3">
-        <v>0.01979710286299567</v>
-      </c>
-      <c r="AQ3">
-        <v>0.1380185633575464</v>
-      </c>
-      <c r="AR3">
-        <v>0.005016331658291476</v>
-      </c>
-      <c r="AS3">
-        <v>0.1509315375982046</v>
-      </c>
-      <c r="AT3">
-        <v>0.009022063055144957</v>
-      </c>
-      <c r="AU3">
         <v>0.02706618916543487</v>
       </c>
     </row>
-    <row r="4" spans="1:47">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>53</v>
       </c>
       <c r="D4">
         <v>406</v>
@@ -1295,90 +1226,72 @@
         <v>-0.02214090274061026</v>
       </c>
       <c r="W4">
-        <v>-0.1237607966652774</v>
+        <v>0.0036</v>
       </c>
       <c r="X4">
-        <v>-0.01197481543232409</v>
+        <v>0.0052</v>
       </c>
       <c r="Y4">
-        <v>0.0036</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="Z4">
-        <v>0.0052</v>
+        <v>-0.11</v>
       </c>
       <c r="AA4">
-        <v>-0.05000000000000004</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.11</v>
+        <v>-0.1230166690346137</v>
       </c>
       <c r="AC4">
-        <v>0.01000000000000001</v>
+        <v>0.02301666903461358</v>
       </c>
       <c r="AD4">
-        <v>-0.1230166690346137</v>
+        <v>0.2012</v>
       </c>
       <c r="AE4">
-        <v>0.02301666903461358</v>
+        <v>0.2164</v>
       </c>
       <c r="AF4">
-        <v>0.2012</v>
+        <v>-0.06764419404435507</v>
       </c>
       <c r="AG4">
-        <v>0.2164</v>
+        <v>-0.1119735373189496</v>
       </c>
       <c r="AH4">
-        <v>-0.06764419404435507</v>
+        <v>-0.0211188354296671</v>
       </c>
       <c r="AI4">
-        <v>-0.1119735373189496</v>
+        <v>0.005</v>
       </c>
       <c r="AJ4">
-        <v>-0.0211188354296671</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AK4">
-        <v>-0.1227389787054995</v>
+        <v>0.04433497536945818</v>
       </c>
       <c r="AL4">
-        <v>-0.009991811914109227</v>
+        <v>-0.01686950701356149</v>
       </c>
       <c r="AM4">
-        <v>0.005</v>
+        <v>0.1050067237163814</v>
       </c>
       <c r="AN4">
-        <v>0.008399999999999999</v>
+        <v>0.1549785601955193</v>
       </c>
       <c r="AO4">
-        <v>0.04433497536945818</v>
-      </c>
-      <c r="AP4">
-        <v>-0.01686950701356149</v>
-      </c>
-      <c r="AQ4">
-        <v>0.1050067237163814</v>
-      </c>
-      <c r="AR4">
-        <v>-0.0304885234225776</v>
-      </c>
-      <c r="AS4">
-        <v>0.1172132467873379</v>
-      </c>
-      <c r="AT4">
-        <v>0.1549785601955193</v>
-      </c>
-      <c r="AU4">
         <v>0.204560421762222</v>
       </c>
     </row>
-    <row r="5" spans="1:47">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D5">
         <v>69</v>
@@ -1438,90 +1351,72 @@
         <v>0.08380091829685227</v>
       </c>
       <c r="W5">
-        <v>-0.1396788216727526</v>
+        <v>0.7464</v>
       </c>
       <c r="X5">
-        <v>0.107729520460603</v>
+        <v>0.9228</v>
       </c>
       <c r="Y5">
-        <v>0.7464</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="Z5">
-        <v>0.9228</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AA5">
-        <v>0.01000000000000001</v>
+        <v>0.09500000000000003</v>
       </c>
       <c r="AB5">
-        <v>-0.08000000000000002</v>
+        <v>-0.09734129388236519</v>
       </c>
       <c r="AC5">
-        <v>0.09500000000000003</v>
+        <v>0.1173412938823652</v>
       </c>
       <c r="AD5">
-        <v>-0.09734129388236519</v>
+        <v>0.8336</v>
       </c>
       <c r="AE5">
-        <v>0.1173412938823652</v>
+        <v>0.8766</v>
       </c>
       <c r="AF5">
-        <v>0.8336</v>
+        <v>-0.01723977231617346</v>
       </c>
       <c r="AG5">
-        <v>0.8766</v>
+        <v>-0.117765501818481</v>
       </c>
       <c r="AH5">
-        <v>-0.01723977231617346</v>
+        <v>0.08218194600946505</v>
       </c>
       <c r="AI5">
-        <v>-0.117765501818481</v>
+        <v>0.751</v>
       </c>
       <c r="AJ5">
-        <v>0.08218194600946505</v>
+        <v>0.9198</v>
       </c>
       <c r="AK5">
-        <v>-0.1403678540165528</v>
+        <v>-0.0434782608695653</v>
       </c>
       <c r="AL5">
-        <v>0.1052342909195122</v>
+        <v>-0.1486789027833803</v>
       </c>
       <c r="AM5">
-        <v>0.751</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="AN5">
-        <v>0.9198</v>
+        <v>0.4104456923623511</v>
       </c>
       <c r="AO5">
-        <v>-0.0434782608695653</v>
-      </c>
-      <c r="AP5">
-        <v>-0.1486789027833803</v>
-      </c>
-      <c r="AQ5">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="AR5">
-        <v>-0.1741545893719806</v>
-      </c>
-      <c r="AS5">
-        <v>0.08108108108108114</v>
-      </c>
-      <c r="AT5">
-        <v>0.4104456923623511</v>
-      </c>
-      <c r="AU5">
         <v>0.8208913847247021</v>
       </c>
     </row>
-    <row r="6" spans="1:47">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>69</v>
@@ -1581,90 +1476,72 @@
         <v>0.06288154246470519</v>
       </c>
       <c r="W6">
-        <v>-0.144290130626136</v>
+        <v>0.5024</v>
       </c>
       <c r="X6">
-        <v>0.08263711906375129</v>
+        <v>0.7744</v>
       </c>
       <c r="Y6">
-        <v>0.5024</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="Z6">
-        <v>0.7744</v>
+        <v>-0.145</v>
       </c>
       <c r="AA6">
-        <v>-0.04000000000000004</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="AB6">
-        <v>-0.145</v>
+        <v>-0.1700413668805986</v>
       </c>
       <c r="AC6">
-        <v>0.06999999999999995</v>
+        <v>0.09004136688059849</v>
       </c>
       <c r="AD6">
-        <v>-0.1700413668805986</v>
+        <v>0.5732</v>
       </c>
       <c r="AE6">
-        <v>0.09004136688059849</v>
+        <v>0.7028</v>
       </c>
       <c r="AF6">
-        <v>0.5732</v>
+        <v>-0.03108205860070312</v>
       </c>
       <c r="AG6">
-        <v>0.7028</v>
+        <v>-0.1262655503625984</v>
       </c>
       <c r="AH6">
-        <v>-0.03108205860070312</v>
+        <v>0.06957054598927924</v>
       </c>
       <c r="AI6">
-        <v>-0.1262655503625984</v>
+        <v>0.5556</v>
       </c>
       <c r="AJ6">
-        <v>0.06957054598927924</v>
+        <v>0.8274</v>
       </c>
       <c r="AK6">
-        <v>-0.1469898117459688</v>
+        <v>0.01449275362318836</v>
       </c>
       <c r="AL6">
-        <v>0.08947643166486603</v>
+        <v>-0.1475963668586618</v>
       </c>
       <c r="AM6">
-        <v>0.5556</v>
+        <v>0.1803392531876139</v>
       </c>
       <c r="AN6">
-        <v>0.8274</v>
+        <v>0.8633641527524397</v>
       </c>
       <c r="AO6">
-        <v>0.01449275362318836</v>
-      </c>
-      <c r="AP6">
-        <v>-0.1475963668586618</v>
-      </c>
-      <c r="AQ6">
-        <v>0.1803392531876139</v>
-      </c>
-      <c r="AR6">
-        <v>-0.1818181818181818</v>
-      </c>
-      <c r="AS6">
-        <v>0.2205882352941176</v>
-      </c>
-      <c r="AT6">
         <v>0.8633641527524397</v>
       </c>
-      <c r="AU6">
-        <v>0.8633641527524397</v>
-      </c>
-    </row>
-    <row r="7" spans="1:47">
+    </row>
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>69</v>
@@ -1724,90 +1601,72 @@
         <v>0.100814865669678</v>
       </c>
       <c r="W7">
-        <v>-0.1614748457486424</v>
+        <v>0.8066</v>
       </c>
       <c r="X7">
-        <v>0.1308031113881423</v>
+        <v>0.9228</v>
       </c>
       <c r="Y7">
-        <v>0.8066</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="Z7">
-        <v>0.9228</v>
+        <v>-0.17</v>
       </c>
       <c r="AA7">
-        <v>-0.05000000000000004</v>
+        <v>0.06</v>
       </c>
       <c r="AB7">
-        <v>-0.17</v>
+        <v>-0.1850000000000001</v>
       </c>
       <c r="AC7">
-        <v>0.06</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="AD7">
-        <v>-0.1850000000000001</v>
+        <v>0.4592</v>
       </c>
       <c r="AE7">
-        <v>0.08500000000000002</v>
+        <v>0.6756</v>
       </c>
       <c r="AF7">
-        <v>0.4592</v>
+        <v>-0.01384228628452966</v>
       </c>
       <c r="AG7">
-        <v>0.6756</v>
+        <v>-0.1354366941567308</v>
       </c>
       <c r="AH7">
-        <v>-0.01384228628452966</v>
+        <v>0.1085662294439589</v>
       </c>
       <c r="AI7">
-        <v>-0.1354366941567308</v>
+        <v>0.8346</v>
       </c>
       <c r="AJ7">
-        <v>0.1085662294439589</v>
+        <v>0.9198</v>
       </c>
       <c r="AK7">
-        <v>-0.1629424849920504</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="AL7">
-        <v>0.1368814188906857</v>
+        <v>-0.07142857142857142</v>
       </c>
       <c r="AM7">
-        <v>0.8346</v>
+        <v>0.1940298507462687</v>
       </c>
       <c r="AN7">
-        <v>0.9198</v>
+        <v>0.3988546137823287</v>
       </c>
       <c r="AO7">
-        <v>0.05797101449275366</v>
-      </c>
-      <c r="AP7">
-        <v>-0.07142857142857142</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1940298507462687</v>
-      </c>
-      <c r="AR7">
-        <v>-0.1050316598824059</v>
-      </c>
-      <c r="AS7">
-        <v>0.2277272727272732</v>
-      </c>
-      <c r="AT7">
-        <v>0.3988546137823287</v>
-      </c>
-      <c r="AU7">
         <v>0.7977092275646573</v>
       </c>
     </row>
-    <row r="8" spans="1:47">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8">
         <v>238</v>
@@ -1867,90 +1726,72 @@
         <v>0.02961214099715429</v>
       </c>
       <c r="W8">
-        <v>-0.06924639598959506</v>
+        <v>0.503</v>
       </c>
       <c r="X8">
-        <v>0.04019670930361872</v>
+        <v>0.503</v>
       </c>
       <c r="Y8">
-        <v>0.503</v>
+        <v>-0.04500000000000004</v>
       </c>
       <c r="Z8">
-        <v>0.503</v>
+        <v>-0.105</v>
       </c>
       <c r="AA8">
-        <v>-0.04500000000000004</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB8">
-        <v>-0.105</v>
+        <v>-0.131897207526139</v>
       </c>
       <c r="AC8">
-        <v>0.03999999999999998</v>
+        <v>0.04189720752613892</v>
       </c>
       <c r="AD8">
-        <v>-0.131897207526139</v>
+        <v>0.3164</v>
       </c>
       <c r="AE8">
-        <v>0.04189720752613892</v>
+        <v>0.3292</v>
       </c>
       <c r="AF8">
-        <v>0.3164</v>
+        <v>-0.01513592838370859</v>
       </c>
       <c r="AG8">
-        <v>0.3292</v>
+        <v>-0.05940962551562724</v>
       </c>
       <c r="AH8">
-        <v>-0.01513592838370859</v>
+        <v>0.02955483342924571</v>
       </c>
       <c r="AI8">
-        <v>-0.05940962551562724</v>
+        <v>0.5008</v>
       </c>
       <c r="AJ8">
-        <v>0.02955483342924571</v>
+        <v>0.5008</v>
       </c>
       <c r="AK8">
-        <v>-0.06892480197736342</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="AL8">
-        <v>0.04023956149928003</v>
+        <v>-0.008298755186721992</v>
       </c>
       <c r="AM8">
-        <v>0.5008</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AN8">
-        <v>0.5008</v>
+        <v>0.0785432549942764</v>
       </c>
       <c r="AO8">
-        <v>0.06302521008403361</v>
-      </c>
-      <c r="AP8">
-        <v>-0.008298755186721992</v>
-      </c>
-      <c r="AQ8">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="AR8">
-        <v>-0.0212179949513163</v>
-      </c>
-      <c r="AS8">
-        <v>0.1483633705869293</v>
-      </c>
-      <c r="AT8">
-        <v>0.0785432549942764</v>
-      </c>
-      <c r="AU8">
         <v>0.1570865099885528</v>
       </c>
     </row>
-    <row r="9" spans="1:47">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <v>238</v>
@@ -2010,90 +1851,72 @@
         <v>-0.03734422411782519</v>
       </c>
       <c r="W9">
-        <v>-0.1735680846859624</v>
+        <v>0.0032</v>
       </c>
       <c r="X9">
-        <v>-0.02302037088749732</v>
+        <v>0.0058</v>
       </c>
       <c r="Y9">
-        <v>0.0032</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="Z9">
-        <v>0.0058</v>
+        <v>-0.16</v>
       </c>
       <c r="AA9">
-        <v>-0.08000000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>-0.16</v>
+        <v>-0.1748543278868911</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>0.01485432788689105</v>
       </c>
       <c r="AD9">
-        <v>-0.1748543278868911</v>
+        <v>0.0716</v>
       </c>
       <c r="AE9">
-        <v>0.01485432788689105</v>
+        <v>0.125</v>
       </c>
       <c r="AF9">
-        <v>0.0716</v>
+        <v>-0.1005471804430421</v>
       </c>
       <c r="AG9">
-        <v>0.125</v>
+        <v>-0.1598467389143226</v>
       </c>
       <c r="AH9">
-        <v>-0.1005471804430421</v>
+        <v>-0.03791708938899847</v>
       </c>
       <c r="AI9">
-        <v>-0.1598467389143226</v>
+        <v>0.0042</v>
       </c>
       <c r="AJ9">
-        <v>-0.03791708938899847</v>
+        <v>0.0114</v>
       </c>
       <c r="AK9">
-        <v>-0.173472335352231</v>
+        <v>0.1008403361344539</v>
       </c>
       <c r="AL9">
-        <v>-0.02353042056685119</v>
+        <v>0.02574557059535602</v>
       </c>
       <c r="AM9">
-        <v>0.0042</v>
+        <v>0.1769547325102881</v>
       </c>
       <c r="AN9">
-        <v>0.0114</v>
+        <v>0.01051393361055575</v>
       </c>
       <c r="AO9">
-        <v>0.1008403361344539</v>
-      </c>
-      <c r="AP9">
-        <v>0.02574557059535602</v>
-      </c>
-      <c r="AQ9">
-        <v>0.1769547325102881</v>
-      </c>
-      <c r="AR9">
-        <v>0.008498016588532281</v>
-      </c>
-      <c r="AS9">
-        <v>0.1965811965811965</v>
-      </c>
-      <c r="AT9">
-        <v>0.01051393361055575</v>
-      </c>
-      <c r="AU9">
         <v>0.03154180083166726</v>
       </c>
     </row>
-    <row r="10" spans="1:47">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>238</v>
@@ -2153,90 +1976,72 @@
         <v>-0.02545425540213038</v>
       </c>
       <c r="W10">
-        <v>-0.157354026556972</v>
+        <v>0.0092</v>
       </c>
       <c r="X10">
-        <v>-0.01043630456801225</v>
+        <v>0.0178</v>
       </c>
       <c r="Y10">
-        <v>0.0092</v>
+        <v>-0.03499999999999998</v>
       </c>
       <c r="Z10">
-        <v>0.0178</v>
+        <v>-0.13</v>
       </c>
       <c r="AA10">
-        <v>-0.03499999999999998</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AB10">
-        <v>-0.13</v>
+        <v>-0.145</v>
       </c>
       <c r="AC10">
-        <v>0.04999999999999999</v>
+        <v>0.07500000000000001</v>
       </c>
       <c r="AD10">
-        <v>-0.145</v>
+        <v>0.454</v>
       </c>
       <c r="AE10">
-        <v>0.07500000000000001</v>
+        <v>0.4868</v>
       </c>
       <c r="AF10">
-        <v>0.454</v>
+        <v>-0.08541125205933353</v>
       </c>
       <c r="AG10">
-        <v>0.4868</v>
+        <v>-0.1444532979412127</v>
       </c>
       <c r="AH10">
-        <v>-0.08541125205933353</v>
+        <v>-0.0259623222200178</v>
       </c>
       <c r="AI10">
-        <v>-0.1444532979412127</v>
+        <v>0.0078</v>
       </c>
       <c r="AJ10">
-        <v>-0.0259623222200178</v>
+        <v>0.0204</v>
       </c>
       <c r="AK10">
-        <v>-0.1571408854458069</v>
+        <v>0.03781512605042026</v>
       </c>
       <c r="AL10">
-        <v>-0.009901327367602573</v>
+        <v>-0.04166666666666666</v>
       </c>
       <c r="AM10">
-        <v>0.0078</v>
+        <v>0.1174456345342423</v>
       </c>
       <c r="AN10">
-        <v>0.0204</v>
+        <v>0.3611297063274773</v>
       </c>
       <c r="AO10">
-        <v>0.03781512605042026</v>
-      </c>
-      <c r="AP10">
-        <v>-0.04166666666666666</v>
-      </c>
-      <c r="AQ10">
-        <v>0.1174456345342423</v>
-      </c>
-      <c r="AR10">
-        <v>-0.0595744680851064</v>
-      </c>
-      <c r="AS10">
-        <v>0.1346938775510204</v>
-      </c>
-      <c r="AT10">
         <v>0.3611297063274773</v>
       </c>
-      <c r="AU10">
-        <v>0.3611297063274773</v>
-      </c>
-    </row>
-    <row r="11" spans="1:47">
+    </row>
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D11">
         <v>99</v>
@@ -2296,90 +2101,72 @@
         <v>0.05111977716054127</v>
       </c>
       <c r="W11">
-        <v>-0.09287133053075676</v>
+        <v>0.6614</v>
       </c>
       <c r="X11">
-        <v>0.06492253544918662</v>
+        <v>0.6614</v>
       </c>
       <c r="Y11">
-        <v>0.6614</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="Z11">
-        <v>0.6614</v>
+        <v>-0.11</v>
       </c>
       <c r="AA11">
-        <v>0.01000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AB11">
-        <v>-0.11</v>
+        <v>-0.114656049457789</v>
       </c>
       <c r="AC11">
-        <v>0.11</v>
+        <v>0.134656049457789</v>
       </c>
       <c r="AD11">
-        <v>-0.114656049457789</v>
+        <v>0.9892</v>
       </c>
       <c r="AE11">
-        <v>0.134656049457789</v>
+        <v>0.9892</v>
       </c>
       <c r="AF11">
-        <v>0.9892</v>
+        <v>-0.01425285713497848</v>
       </c>
       <c r="AG11">
-        <v>0.9892</v>
+        <v>-0.08059016955817802</v>
       </c>
       <c r="AH11">
-        <v>-0.01425285713497848</v>
+        <v>0.05341654811530116</v>
       </c>
       <c r="AI11">
-        <v>-0.08059016955817802</v>
+        <v>0.6748</v>
       </c>
       <c r="AJ11">
-        <v>0.05341654811530116</v>
+        <v>0.6748</v>
       </c>
       <c r="AK11">
-        <v>-0.09379365909437119</v>
+        <v>0.02020202020202011</v>
       </c>
       <c r="AL11">
-        <v>0.06854289563696495</v>
+        <v>-0.09900990099009901</v>
       </c>
       <c r="AM11">
-        <v>0.6748</v>
+        <v>0.1320754716981132</v>
       </c>
       <c r="AN11">
-        <v>0.6748</v>
+        <v>0.7329150910757301</v>
       </c>
       <c r="AO11">
-        <v>0.02020202020202011</v>
-      </c>
-      <c r="AP11">
-        <v>-0.09900990099009901</v>
-      </c>
-      <c r="AQ11">
-        <v>0.1320754716981132</v>
-      </c>
-      <c r="AR11">
-        <v>-0.1254247572815532</v>
-      </c>
-      <c r="AS11">
-        <v>0.1601320754716982</v>
-      </c>
-      <c r="AT11">
         <v>0.7329150910757301</v>
       </c>
-      <c r="AU11">
-        <v>0.7329150910757301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:47">
+    </row>
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>99</v>
@@ -2439,90 +2226,72 @@
         <v>-0.01656233111272169</v>
       </c>
       <c r="W12">
-        <v>-0.1608339457403495</v>
+        <v>0.0324</v>
       </c>
       <c r="X12">
-        <v>-0.004960680388902138</v>
+        <v>0.0764</v>
       </c>
       <c r="Y12">
-        <v>0.0324</v>
+        <v>-0.03999999999999998</v>
       </c>
       <c r="Z12">
-        <v>0.0764</v>
+        <v>-0.12</v>
       </c>
       <c r="AA12">
-        <v>-0.03999999999999998</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AB12">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AC12">
-        <v>0.04999999999999999</v>
+        <v>0.06000000000000004</v>
       </c>
       <c r="AD12">
-        <v>-0.14</v>
+        <v>0.6532</v>
       </c>
       <c r="AE12">
-        <v>0.06000000000000004</v>
+        <v>0.7156</v>
       </c>
       <c r="AF12">
-        <v>0.6532</v>
+        <v>-0.07274264322691626</v>
       </c>
       <c r="AG12">
-        <v>0.7156</v>
+        <v>-0.1326539191798262</v>
       </c>
       <c r="AH12">
-        <v>-0.07274264322691626</v>
+        <v>-0.01153379621125429</v>
       </c>
       <c r="AI12">
-        <v>-0.1326539191798262</v>
+        <v>0.029</v>
       </c>
       <c r="AJ12">
-        <v>-0.01153379621125429</v>
+        <v>0.0992</v>
       </c>
       <c r="AK12">
-        <v>-0.1432527526244144</v>
+        <v>0.07070707070707061</v>
       </c>
       <c r="AL12">
-        <v>0.001523501976089357</v>
+        <v>-0.0396039603960396</v>
       </c>
       <c r="AM12">
-        <v>0.029</v>
+        <v>0.1747572815533981</v>
       </c>
       <c r="AN12">
-        <v>0.0992</v>
+        <v>0.2080477461314518</v>
       </c>
       <c r="AO12">
-        <v>0.07070707070707061</v>
-      </c>
-      <c r="AP12">
-        <v>-0.0396039603960396</v>
-      </c>
-      <c r="AQ12">
-        <v>0.1747572815533981</v>
-      </c>
-      <c r="AR12">
-        <v>-0.06122448979591832</v>
-      </c>
-      <c r="AS12">
-        <v>0.2</v>
-      </c>
-      <c r="AT12">
-        <v>0.2080477461314518</v>
-      </c>
-      <c r="AU12">
         <v>0.6241432383943554</v>
       </c>
     </row>
-    <row r="13" spans="1:47">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>99</v>
@@ -2582,78 +2351,60 @@
         <v>0.01365989588905082</v>
       </c>
       <c r="W13">
-        <v>-0.1757994104417805</v>
+        <v>0.1566</v>
       </c>
       <c r="X13">
-        <v>0.02953438105763693</v>
+        <v>0.2464</v>
       </c>
       <c r="Y13">
-        <v>0.1566</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="Z13">
-        <v>0.2464</v>
+        <v>-0.16</v>
       </c>
       <c r="AA13">
-        <v>-0.04999999999999999</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="AB13">
-        <v>-0.16</v>
+        <v>-0.1935531761552672</v>
       </c>
       <c r="AC13">
-        <v>0.08500000000000002</v>
+        <v>0.09355317615526718</v>
       </c>
       <c r="AD13">
-        <v>-0.1935531761552672</v>
+        <v>0.6528</v>
       </c>
       <c r="AE13">
-        <v>0.09355317615526718</v>
+        <v>0.7156</v>
       </c>
       <c r="AF13">
-        <v>0.6528</v>
+        <v>-0.05848978609193778</v>
       </c>
       <c r="AG13">
-        <v>0.7156</v>
+        <v>-0.1360691728962422</v>
       </c>
       <c r="AH13">
-        <v>-0.05848978609193778</v>
+        <v>0.01505136763452953</v>
       </c>
       <c r="AI13">
-        <v>-0.1360691728962422</v>
+        <v>0.148</v>
       </c>
       <c r="AJ13">
-        <v>0.01505136763452953</v>
+        <v>0.2186</v>
       </c>
       <c r="AK13">
-        <v>-0.1521339969166954</v>
+        <v>0.0505050505050505</v>
       </c>
       <c r="AL13">
-        <v>0.03162738926570315</v>
+        <v>-0.0721930646672914</v>
       </c>
       <c r="AM13">
-        <v>0.148</v>
+        <v>0.1739552553820179</v>
       </c>
       <c r="AN13">
-        <v>0.2186</v>
+        <v>0.4273643299212784</v>
       </c>
       <c r="AO13">
-        <v>0.0505050505050505</v>
-      </c>
-      <c r="AP13">
-        <v>-0.0721930646672914</v>
-      </c>
-      <c r="AQ13">
-        <v>0.1739552553820179</v>
-      </c>
-      <c r="AR13">
-        <v>-0.09999999999999998</v>
-      </c>
-      <c r="AS13">
-        <v>0.2021276595744681</v>
-      </c>
-      <c r="AT13">
-        <v>0.4273643299212784</v>
-      </c>
-      <c r="AU13">
         <v>0.7329150910757301</v>
       </c>
     </row>
@@ -2673,130 +2424,130 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2814,48 +2565,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
         <v>84</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>87</v>
-      </c>
-      <c r="E1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E2">
         <v>0.02049261083743842</v>
@@ -2873,21 +2624,21 @@
         <v>250</v>
       </c>
       <c r="J2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E3">
         <v>0.02807881773399015</v>
@@ -2905,21 +2656,21 @@
         <v>250</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E4">
         <v>0.04536945812807881</v>
@@ -2937,21 +2688,21 @@
         <v>250</v>
       </c>
       <c r="J4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E5">
         <v>0.4010837438423646</v>
@@ -2969,21 +2720,21 @@
         <v>250</v>
       </c>
       <c r="J5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>0.413743842364532</v>
@@ -3001,21 +2752,21 @@
         <v>250</v>
       </c>
       <c r="J6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>0.4725615763546798</v>
@@ -3033,21 +2784,21 @@
         <v>250</v>
       </c>
       <c r="J7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E8">
         <v>0.503346436828533</v>
@@ -3065,21 +2816,21 @@
         <v>250</v>
       </c>
       <c r="J8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E9">
         <v>0.5190271308530763</v>
@@ -3097,21 +2848,21 @@
         <v>250</v>
       </c>
       <c r="J9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E10">
         <v>0.5875820873372553</v>
@@ -3129,21 +2880,21 @@
         <v>250</v>
       </c>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E11">
         <v>0.34</v>
@@ -3161,21 +2912,21 @@
         <v>250</v>
       </c>
       <c r="J11" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E12">
         <v>0.35</v>
@@ -3193,21 +2944,21 @@
         <v>250</v>
       </c>
       <c r="J12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
         <v>47</v>
       </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E13">
         <v>0.4</v>
@@ -3225,21 +2976,21 @@
         <v>250</v>
       </c>
       <c r="J13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E14">
         <v>0.5035496260262651</v>
@@ -3257,21 +3008,21 @@
         <v>250</v>
       </c>
       <c r="J14" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E15">
         <v>0.5189064985777815</v>
@@ -3289,21 +3040,21 @@
         <v>250</v>
       </c>
       <c r="J15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E16">
         <v>0.5865506926221365</v>
@@ -3321,21 +3072,21 @@
         <v>250</v>
       </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E17">
         <v>0.6921182266009852</v>
@@ -3353,21 +3104,21 @@
         <v>250</v>
       </c>
       <c r="J17" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E18">
         <v>0.6576354679802956</v>
@@ -3385,21 +3136,21 @@
         <v>250</v>
       </c>
       <c r="J18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
         <v>47</v>
       </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E19">
         <v>0.6133004926108374</v>
@@ -3417,21 +3168,21 @@
         <v>250</v>
       </c>
       <c r="J19" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E20">
         <v>0.01043478260869565</v>
@@ -3449,21 +3200,21 @@
         <v>44</v>
       </c>
       <c r="J20" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E21">
         <v>0.01811594202898551</v>
@@ -3481,21 +3232,21 @@
         <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>0.06304347826086956</v>
@@ -3513,21 +3264,21 @@
         <v>44</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E23">
         <v>0.4165217391304348</v>
@@ -3545,21 +3296,21 @@
         <v>44</v>
       </c>
       <c r="J23" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E24">
         <v>0.4256521739130435</v>
@@ -3577,21 +3328,21 @@
         <v>44</v>
       </c>
       <c r="J24" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>0.4534782608695653</v>
@@ -3609,21 +3360,21 @@
         <v>44</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E26">
         <v>0.5201170436838566</v>
@@ -3641,21 +3392,21 @@
         <v>44</v>
       </c>
       <c r="J26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E27">
         <v>0.5374321662622487</v>
@@ -3673,21 +3424,21 @@
         <v>44</v>
       </c>
       <c r="J27" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E28">
         <v>0.5544640969283843</v>
@@ -3705,21 +3456,21 @@
         <v>44</v>
       </c>
       <c r="J28" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E29">
         <v>0.36</v>
@@ -3737,21 +3488,21 @@
         <v>44</v>
       </c>
       <c r="J29" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E30">
         <v>0.35</v>
@@ -3769,21 +3520,21 @@
         <v>44</v>
       </c>
       <c r="J30" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E31">
         <v>0.4</v>
@@ -3801,21 +3552,21 @@
         <v>44</v>
       </c>
       <c r="J31" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E32">
         <v>0.5238220251826913</v>
@@ -3833,21 +3584,21 @@
         <v>44</v>
       </c>
       <c r="J32" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E33">
         <v>0.5410617974988647</v>
@@ -3865,21 +3616,21 @@
         <v>44</v>
       </c>
       <c r="J33" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E34">
         <v>0.5549040837833944</v>
@@ -3897,21 +3648,21 @@
         <v>44</v>
       </c>
       <c r="J34" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" t="s">
         <v>94</v>
-      </c>
-      <c r="C35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" t="s">
-        <v>100</v>
       </c>
       <c r="E35">
         <v>0.6666666666666666</v>
@@ -3929,21 +3680,21 @@
         <v>44</v>
       </c>
       <c r="J35" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" t="s">
         <v>94</v>
-      </c>
-      <c r="C36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" t="s">
-        <v>100</v>
       </c>
       <c r="E36">
         <v>0.7101449275362319</v>
@@ -3961,21 +3712,21 @@
         <v>44</v>
       </c>
       <c r="J36" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
         <v>94</v>
-      </c>
-      <c r="C37" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" t="s">
-        <v>100</v>
       </c>
       <c r="E37">
         <v>0.6521739130434783</v>
@@ -3993,21 +3744,21 @@
         <v>44</v>
       </c>
       <c r="J37" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>0.01693277310924369</v>
@@ -4025,21 +3776,21 @@
         <v>154</v>
       </c>
       <c r="J38" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E39">
         <v>0.01974789915966386</v>
@@ -4057,21 +3808,21 @@
         <v>154</v>
       </c>
       <c r="J39" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>0.01130252100840337</v>
@@ -4089,21 +3840,21 @@
         <v>154</v>
       </c>
       <c r="J40" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>0.3740756302521008</v>
@@ -4121,21 +3872,21 @@
         <v>154</v>
       </c>
       <c r="J41" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E42">
         <v>0.3876470588235295</v>
@@ -4153,21 +3904,21 @@
         <v>154</v>
       </c>
       <c r="J42" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E43">
         <v>0.4584453781512605</v>
@@ -4185,21 +3936,21 @@
         <v>154</v>
       </c>
       <c r="J43" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>0.4805271090386144</v>
@@ -4217,21 +3968,21 @@
         <v>154</v>
       </c>
       <c r="J44" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E45">
         <v>0.4957262730732819</v>
@@ -4249,21 +4000,21 @@
         <v>154</v>
       </c>
       <c r="J45" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E46">
         <v>0.5806744123080022</v>
@@ -4281,21 +4032,21 @@
         <v>154</v>
       </c>
       <c r="J46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E47">
         <v>0.29</v>
@@ -4313,21 +4064,21 @@
         <v>154</v>
       </c>
       <c r="J47" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E48">
         <v>0.335</v>
@@ -4345,21 +4096,21 @@
         <v>154</v>
       </c>
       <c r="J48" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E49">
         <v>0.37</v>
@@ -4377,21 +4128,21 @@
         <v>154</v>
       </c>
       <c r="J49" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E50">
         <v>0.4812407527715649</v>
@@ -4409,21 +4160,21 @@
         <v>154</v>
       </c>
       <c r="J50" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E51">
         <v>0.4963766811552734</v>
@@ -4441,21 +4192,21 @@
         <v>154</v>
       </c>
       <c r="J51" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E52">
         <v>0.581787933214607</v>
@@ -4473,21 +4224,21 @@
         <v>154</v>
       </c>
       <c r="J52" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" t="s">
         <v>94</v>
-      </c>
-      <c r="C53" t="s">
-        <v>51</v>
-      </c>
-      <c r="D53" t="s">
-        <v>100</v>
       </c>
       <c r="E53">
         <v>0.7394957983193278</v>
@@ -4505,21 +4256,21 @@
         <v>154</v>
       </c>
       <c r="J53" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" t="s">
         <v>94</v>
-      </c>
-      <c r="C54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D54" t="s">
-        <v>100</v>
       </c>
       <c r="E54">
         <v>0.6764705882352942</v>
@@ -4537,21 +4288,21 @@
         <v>154</v>
       </c>
       <c r="J54" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
         <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>53</v>
-      </c>
-      <c r="D55" t="s">
-        <v>100</v>
       </c>
       <c r="E55">
         <v>0.6386554621848739</v>
@@ -4569,21 +4320,21 @@
         <v>154</v>
       </c>
       <c r="J55" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E56">
         <v>0.03606060606060607</v>
@@ -4601,21 +4352,21 @@
         <v>64</v>
       </c>
       <c r="J56" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E57">
         <v>0.05505050505050505</v>
@@ -4633,21 +4384,21 @@
         <v>64</v>
       </c>
       <c r="J57" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D58" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E58">
         <v>0.1149494949494949</v>
@@ -4665,21 +4416,21 @@
         <v>64</v>
       </c>
       <c r="J58" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D59" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E59">
         <v>0.4552525252525252</v>
@@ -4697,21 +4448,21 @@
         <v>64</v>
       </c>
       <c r="J59" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D60" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E60">
         <v>0.4681818181818182</v>
@@ -4729,21 +4480,21 @@
         <v>64</v>
       </c>
       <c r="J60" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E61">
         <v>0.5197979797979798</v>
@@ -4761,21 +4512,21 @@
         <v>64</v>
       </c>
       <c r="J61" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E62">
         <v>0.543478322353971</v>
@@ -4793,21 +4544,21 @@
         <v>64</v>
       </c>
       <c r="J62" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E63">
         <v>0.559177787452075</v>
@@ -4825,21 +4576,21 @@
         <v>64</v>
       </c>
       <c r="J63" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E64">
         <v>0.6253112356372157</v>
@@ -4857,21 +4608,21 @@
         <v>64</v>
       </c>
       <c r="J64" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E65">
         <v>0.45</v>
@@ -4889,21 +4640,21 @@
         <v>64</v>
       </c>
       <c r="J65" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D66" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E66">
         <v>0.44</v>
@@ -4921,21 +4672,21 @@
         <v>64</v>
       </c>
       <c r="J66" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C67" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E67">
         <v>0.49</v>
@@ -4953,21 +4704,21 @@
         <v>64</v>
       </c>
       <c r="J67" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D68" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E68">
         <v>0.5450403807953941</v>
@@ -4985,21 +4736,21 @@
         <v>64</v>
       </c>
       <c r="J68" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E69">
         <v>0.5592932379303726</v>
@@ -5017,21 +4768,21 @@
         <v>64</v>
       </c>
       <c r="J69" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E70">
         <v>0.6177830240223103</v>
@@ -5049,21 +4800,21 @@
         <v>64</v>
       </c>
       <c r="J70" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" t="s">
         <v>94</v>
-      </c>
-      <c r="C71" t="s">
-        <v>51</v>
-      </c>
-      <c r="D71" t="s">
-        <v>100</v>
       </c>
       <c r="E71">
         <v>0.5959595959595959</v>
@@ -5081,21 +4832,21 @@
         <v>64</v>
       </c>
       <c r="J71" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" t="s">
         <v>94</v>
-      </c>
-      <c r="C72" t="s">
-        <v>52</v>
-      </c>
-      <c r="D72" t="s">
-        <v>100</v>
       </c>
       <c r="E72">
         <v>0.5757575757575758</v>
@@ -5113,21 +4864,21 @@
         <v>64</v>
       </c>
       <c r="J72" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" t="s">
+        <v>47</v>
+      </c>
+      <c r="D73" t="s">
         <v>94</v>
-      </c>
-      <c r="C73" t="s">
-        <v>53</v>
-      </c>
-      <c r="D73" t="s">
-        <v>100</v>
       </c>
       <c r="E73">
         <v>0.5252525252525253</v>
@@ -5145,7 +4896,7 @@
         <v>64</v>
       </c>
       <c r="J73" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -5168,78 +4919,78 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" t="s">
         <v>84</v>
       </c>
-      <c r="B1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" t="s">
         <v>102</v>
       </c>
-      <c r="E1" t="s">
+      <c r="M1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" t="s">
+      <c r="N1" t="s">
         <v>104</v>
       </c>
-      <c r="G1" t="s">
+      <c r="O1" t="s">
         <v>105</v>
       </c>
-      <c r="H1" t="s">
+      <c r="P1" t="s">
         <v>106</v>
       </c>
-      <c r="I1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>107</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>108</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>109</v>
-      </c>
-      <c r="N1" t="s">
-        <v>110</v>
-      </c>
-      <c r="O1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R1" t="s">
-        <v>114</v>
-      </c>
-      <c r="S1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F2">
         <v>0.02049261083743842</v>
@@ -5266,13 +5017,13 @@
         <v>1.530907631213612</v>
       </c>
       <c r="N2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O2">
         <v>0.7454</v>
       </c>
       <c r="P2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q2">
         <v>-0.05410272103966406</v>
@@ -5281,24 +5032,24 @@
         <v>0.03893030724656057</v>
       </c>
       <c r="S2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>0.4010837438423646</v>
@@ -5325,13 +5076,13 @@
         <v>1.455610834346575</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O3">
         <v>0.461</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q3">
         <v>-0.05229618964656447</v>
@@ -5340,24 +5091,24 @@
         <v>0.02697599260222917</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>0.503346436828533</v>
@@ -5384,39 +5135,33 @@
         <v>1.525496624127441</v>
       </c>
       <c r="N4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O4">
         <v>0.3852</v>
       </c>
       <c r="P4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q4">
-        <v>-0.05856576544801699</v>
-      </c>
-      <c r="R4">
-        <v>0.02781683152088923</v>
+        <v>110</v>
       </c>
       <c r="S4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F5">
         <v>0.34</v>
@@ -5437,13 +5182,13 @@
         <v>0.6968</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O5">
         <v>0.844</v>
       </c>
       <c r="P5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q5">
         <v>-0.08000000000000002</v>
@@ -5452,24 +5197,24 @@
         <v>0.06000000000000011</v>
       </c>
       <c r="S5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>0.5035496260262651</v>
@@ -5490,39 +5235,33 @@
         <v>0.3894</v>
       </c>
       <c r="N6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O6">
         <v>0.3894</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q6">
-        <v>-0.05815433485882694</v>
-      </c>
-      <c r="R6">
-        <v>0.02825025172545625</v>
+        <v>110</v>
       </c>
       <c r="S6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>0.6921182266009852</v>
@@ -5549,39 +5288,33 @@
         <v>1.575352047426485</v>
       </c>
       <c r="N7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O7">
         <v>0.204560421762222</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="R7">
-        <v>0.09762516046213096</v>
+        <v>111</v>
       </c>
       <c r="S7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
         <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
       </c>
       <c r="F8">
         <v>0.02049261083743842</v>
@@ -5608,13 +5341,13 @@
         <v>1.496102394400772</v>
       </c>
       <c r="N8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O8">
         <v>0.5734</v>
       </c>
       <c r="P8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q8">
         <v>-0.08440726271056505</v>
@@ -5623,24 +5356,24 @@
         <v>0.03465356812928412</v>
       </c>
       <c r="S8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
         <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" t="s">
-        <v>53</v>
       </c>
       <c r="F9">
         <v>0.4010837438423646</v>
@@ -5667,13 +5400,13 @@
         <v>1.553586372596406</v>
       </c>
       <c r="N9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O9">
         <v>0.0004</v>
       </c>
       <c r="P9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>-0.1160939316204946</v>
@@ -5682,24 +5415,24 @@
         <v>-0.02686173340413649</v>
       </c>
       <c r="S9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
         <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
       </c>
       <c r="F10">
         <v>0.503346436828533</v>
@@ -5726,39 +5459,33 @@
         <v>1.581607874494274</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O10">
         <v>0.0008</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q10">
-        <v>-0.1343146850892963</v>
-      </c>
-      <c r="R10">
-        <v>-0.03239054644227168</v>
+        <v>110</v>
       </c>
       <c r="S10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
       </c>
       <c r="F11">
         <v>0.34</v>
@@ -5779,13 +5506,13 @@
         <v>0.0392</v>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O11">
         <v>0.09859999999999999</v>
       </c>
       <c r="P11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q11">
         <v>-0.1280741611297382</v>
@@ -5794,24 +5521,24 @@
         <v>0.008074161129738258</v>
       </c>
       <c r="S11" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>53</v>
       </c>
       <c r="F12">
         <v>0.5035496260262651</v>
@@ -5832,39 +5559,33 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="N12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O12">
         <v>0.0008</v>
       </c>
       <c r="P12" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q12">
-        <v>-0.1324121069898527</v>
-      </c>
-      <c r="R12">
-        <v>-0.03081160526701515</v>
+        <v>110</v>
       </c>
       <c r="S12" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
         <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>53</v>
       </c>
       <c r="F13">
         <v>0.6921182266009852</v>
@@ -5891,39 +5612,33 @@
         <v>1.513247813472457</v>
       </c>
       <c r="N13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O13">
         <v>0.02706618916543487</v>
       </c>
       <c r="P13" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13">
-        <v>0.005016331658291476</v>
-      </c>
-      <c r="R13">
-        <v>0.1509315375982046</v>
+        <v>111</v>
       </c>
       <c r="S13" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
         <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" t="s">
-        <v>53</v>
       </c>
       <c r="F14">
         <v>0.02807881773399015</v>
@@ -5950,13 +5665,13 @@
         <v>1.422466582636034</v>
       </c>
       <c r="N14" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O14">
         <v>0.7454</v>
       </c>
       <c r="P14" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q14">
         <v>-0.08180644473769276</v>
@@ -5965,24 +5680,24 @@
         <v>0.0472251639495153</v>
       </c>
       <c r="S14" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
         <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" t="s">
-        <v>53</v>
       </c>
       <c r="F15">
         <v>0.413743842364532</v>
@@ -6009,13 +5724,13 @@
         <v>1.419611895158891</v>
       </c>
       <c r="N15" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O15">
         <v>0.0104</v>
       </c>
       <c r="P15" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q15">
         <v>-0.1084139624854691</v>
@@ -6024,24 +5739,24 @@
         <v>-0.009221505494826733</v>
       </c>
       <c r="S15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
         <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
-        <v>53</v>
       </c>
       <c r="F16">
         <v>0.5190271308530763</v>
@@ -6068,39 +5783,33 @@
         <v>1.504729680828269</v>
       </c>
       <c r="N16" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O16">
         <v>0.0052</v>
       </c>
       <c r="P16" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q16">
-        <v>-0.1237607966652774</v>
-      </c>
-      <c r="R16">
-        <v>-0.01197481543232409</v>
+        <v>110</v>
       </c>
       <c r="S16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
         <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" t="s">
-        <v>53</v>
       </c>
       <c r="F17">
         <v>0.35</v>
@@ -6121,13 +5830,13 @@
         <v>0.2012</v>
       </c>
       <c r="N17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O17">
         <v>0.2164</v>
       </c>
       <c r="P17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q17">
         <v>-0.1230166690346137</v>
@@ -6136,24 +5845,24 @@
         <v>0.02301666903461358</v>
       </c>
       <c r="S17" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" t="s">
-        <v>53</v>
       </c>
       <c r="F18">
         <v>0.5189064985777815</v>
@@ -6174,39 +5883,33 @@
         <v>0.005</v>
       </c>
       <c r="N18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O18">
         <v>0.008399999999999999</v>
       </c>
       <c r="P18" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q18">
-        <v>-0.1227389787054995</v>
-      </c>
-      <c r="R18">
-        <v>-0.009991811914109227</v>
+        <v>110</v>
       </c>
       <c r="S18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
         <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" t="s">
-        <v>53</v>
       </c>
       <c r="F19">
         <v>0.6576354679802956</v>
@@ -6233,39 +5936,33 @@
         <v>1.425473510706959</v>
       </c>
       <c r="N19" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O19">
         <v>0.204560421762222</v>
       </c>
       <c r="P19" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q19">
-        <v>-0.0304885234225776</v>
-      </c>
-      <c r="R19">
-        <v>0.1172132467873379</v>
+        <v>111</v>
       </c>
       <c r="S19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>0.01043478260869565</v>
@@ -6292,13 +5989,13 @@
         <v>1.336772764287313</v>
       </c>
       <c r="N20" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O20">
         <v>0.8618</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q20">
         <v>-0.1141871619631026</v>
@@ -6307,24 +6004,24 @@
         <v>0.09882484312252289</v>
       </c>
       <c r="S20" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F21">
         <v>0.4165217391304348</v>
@@ -6351,13 +6048,13 @@
         <v>1.26766664491409</v>
       </c>
       <c r="N21" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O21">
         <v>0.8304</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q21">
         <v>-0.1101837620501105</v>
@@ -6366,24 +6063,24 @@
         <v>0.0919228924848931</v>
       </c>
       <c r="S21" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F22">
         <v>0.5201170436838566</v>
@@ -6410,39 +6107,33 @@
         <v>1.374108209799784</v>
       </c>
       <c r="N22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O22">
         <v>0.9228</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q22">
-        <v>-0.1396788216727526</v>
-      </c>
-      <c r="R22">
-        <v>0.107729520460603</v>
+        <v>110</v>
       </c>
       <c r="S22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F23">
         <v>0.36</v>
@@ -6463,13 +6154,13 @@
         <v>0.8336</v>
       </c>
       <c r="N23" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O23">
         <v>0.8766</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q23">
         <v>-0.09734129388236519</v>
@@ -6478,24 +6169,24 @@
         <v>0.1173412938823652</v>
       </c>
       <c r="S23" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F24">
         <v>0.5238220251826913</v>
@@ -6516,39 +6207,33 @@
         <v>0.751</v>
       </c>
       <c r="N24" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O24">
         <v>0.9198</v>
       </c>
       <c r="P24" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q24">
-        <v>-0.1403678540165528</v>
-      </c>
-      <c r="R24">
-        <v>0.1052342909195122</v>
+        <v>110</v>
       </c>
       <c r="S24" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
         <v>94</v>
       </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F25">
         <v>0.6666666666666666</v>
@@ -6575,39 +6260,33 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O25">
         <v>0.8208913847247021</v>
       </c>
       <c r="P25" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q25">
-        <v>-0.1741545893719806</v>
-      </c>
-      <c r="R25">
-        <v>0.08108108108108114</v>
+        <v>111</v>
       </c>
       <c r="S25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F26">
         <v>0.01043478260869565</v>
@@ -6634,13 +6313,13 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N26" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O26">
         <v>0.6546</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q26">
         <v>-0.2000900155857261</v>
@@ -6649,24 +6328,24 @@
         <v>0.09487262428137828</v>
       </c>
       <c r="S26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F27">
         <v>0.4165217391304348</v>
@@ -6693,13 +6372,13 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N27" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O27">
         <v>0.6682</v>
       </c>
       <c r="P27" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q27">
         <v>-0.1410315331593855</v>
@@ -6708,24 +6387,24 @@
         <v>0.06711848968112478</v>
       </c>
       <c r="S27" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F28">
         <v>0.5201170436838566</v>
@@ -6752,39 +6431,33 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O28">
         <v>0.7744</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q28">
-        <v>-0.144290130626136</v>
-      </c>
-      <c r="R28">
-        <v>0.08263711906375129</v>
+        <v>110</v>
       </c>
       <c r="S28" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F29">
         <v>0.36</v>
@@ -6805,13 +6478,13 @@
         <v>0.5732</v>
       </c>
       <c r="N29" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O29">
         <v>0.7028</v>
       </c>
       <c r="P29" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q29">
         <v>-0.1700413668805986</v>
@@ -6820,24 +6493,24 @@
         <v>0.09004136688059849</v>
       </c>
       <c r="S29" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F30">
         <v>0.5238220251826913</v>
@@ -6858,39 +6531,33 @@
         <v>0.5556</v>
       </c>
       <c r="N30" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O30">
         <v>0.8274</v>
       </c>
       <c r="P30" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q30">
-        <v>-0.1469898117459688</v>
-      </c>
-      <c r="R30">
-        <v>0.08947643166486603</v>
+        <v>110</v>
       </c>
       <c r="S30" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
         <v>94</v>
       </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F31">
         <v>0.6666666666666666</v>
@@ -6917,39 +6584,33 @@
         <v>1.473567895472554</v>
       </c>
       <c r="N31" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O31">
         <v>0.8633641527524397</v>
       </c>
       <c r="P31" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q31">
-        <v>-0.1818181818181818</v>
-      </c>
-      <c r="R31">
-        <v>0.2205882352941176</v>
+        <v>111</v>
       </c>
       <c r="S31" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F32">
         <v>0.01811594202898551</v>
@@ -6976,13 +6637,13 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N32" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O32">
         <v>0.7151999999999999</v>
       </c>
       <c r="P32" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q32">
         <v>-0.2027351339597176</v>
@@ -6991,24 +6652,24 @@
         <v>0.1128800614959495</v>
       </c>
       <c r="S32" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F33">
         <v>0.4256521739130435</v>
@@ -7035,13 +6696,13 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N33" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O33">
         <v>0.7912</v>
       </c>
       <c r="P33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q33">
         <v>-0.1503432645023226</v>
@@ -7050,24 +6711,24 @@
         <v>0.09469109058927928</v>
       </c>
       <c r="S33" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F34">
         <v>0.5374321662622487</v>
@@ -7094,39 +6755,33 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N34" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O34">
         <v>0.9228</v>
       </c>
       <c r="P34" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q34">
-        <v>-0.1614748457486424</v>
-      </c>
-      <c r="R34">
-        <v>0.1308031113881423</v>
+        <v>110</v>
       </c>
       <c r="S34" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F35">
         <v>0.35</v>
@@ -7147,13 +6802,13 @@
         <v>0.4592</v>
       </c>
       <c r="N35" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O35">
         <v>0.6756</v>
       </c>
       <c r="P35" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q35">
         <v>-0.1850000000000001</v>
@@ -7162,24 +6817,24 @@
         <v>0.08500000000000002</v>
       </c>
       <c r="S35" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F36">
         <v>0.5410617974988647</v>
@@ -7200,39 +6855,33 @@
         <v>0.8346</v>
       </c>
       <c r="N36" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O36">
         <v>0.9198</v>
       </c>
       <c r="P36" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q36">
-        <v>-0.1629424849920504</v>
-      </c>
-      <c r="R36">
-        <v>0.1368814188906857</v>
+        <v>110</v>
       </c>
       <c r="S36" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" t="s">
         <v>94</v>
       </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F37">
         <v>0.7101449275362319</v>
@@ -7259,39 +6908,33 @@
         <v>1.568181818181818</v>
       </c>
       <c r="N37" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O37">
         <v>0.7977092275646573</v>
       </c>
       <c r="P37" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q37">
-        <v>-0.1050316598824059</v>
-      </c>
-      <c r="R37">
-        <v>0.2277272727272732</v>
+        <v>111</v>
       </c>
       <c r="S37" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F38">
         <v>0.01693277310924369</v>
@@ -7318,13 +6961,13 @@
         <v>1.359032548719953</v>
       </c>
       <c r="N38" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O38">
         <v>0.982</v>
       </c>
       <c r="P38" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q38">
         <v>-0.06625616770219352</v>
@@ -7333,24 +6976,24 @@
         <v>0.06062591560135315</v>
       </c>
       <c r="S38" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:19">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F39">
         <v>0.3740756302521008</v>
@@ -7377,13 +7020,13 @@
         <v>1.345653477740814</v>
       </c>
       <c r="N39" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O39">
         <v>0.5570000000000001</v>
       </c>
       <c r="P39" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q39">
         <v>-0.06891405825293671</v>
@@ -7392,24 +7035,24 @@
         <v>0.04177120111008013</v>
       </c>
       <c r="S39" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F40">
         <v>0.4805271090386144</v>
@@ -7436,39 +7079,33 @@
         <v>1.366375422058099</v>
       </c>
       <c r="N40" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O40">
         <v>0.503</v>
       </c>
       <c r="P40" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q40">
-        <v>-0.06924639598959506</v>
-      </c>
-      <c r="R40">
-        <v>0.04019670930361872</v>
+        <v>110</v>
       </c>
       <c r="S40" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F41">
         <v>0.29</v>
@@ -7489,13 +7126,13 @@
         <v>0.3164</v>
       </c>
       <c r="N41" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O41">
         <v>0.3292</v>
       </c>
       <c r="P41" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q41">
         <v>-0.131897207526139</v>
@@ -7504,24 +7141,24 @@
         <v>0.04189720752613892</v>
       </c>
       <c r="S41" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:19">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F42">
         <v>0.4812407527715649</v>
@@ -7542,39 +7179,33 @@
         <v>0.5008</v>
       </c>
       <c r="N42" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O42">
         <v>0.5008</v>
       </c>
       <c r="P42" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q42">
-        <v>-0.06892480197736342</v>
-      </c>
-      <c r="R42">
-        <v>0.04023956149928003</v>
+        <v>110</v>
       </c>
       <c r="S42" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s">
         <v>94</v>
       </c>
-      <c r="C43" t="s">
-        <v>100</v>
-      </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F43">
         <v>0.7394957983193278</v>
@@ -7601,39 +7232,33 @@
         <v>1.473305902152329</v>
       </c>
       <c r="N43" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O43">
         <v>0.1570865099885528</v>
       </c>
       <c r="P43" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q43">
-        <v>-0.0212179949513163</v>
-      </c>
-      <c r="R43">
-        <v>0.1483633705869293</v>
+        <v>111</v>
       </c>
       <c r="S43" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F44">
         <v>0.01693277310924369</v>
@@ -7660,13 +7285,13 @@
         <v>1.315229181497365</v>
       </c>
       <c r="N44" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O44">
         <v>0.982</v>
       </c>
       <c r="P44" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q44">
         <v>-0.0744154556769744</v>
@@ -7675,24 +7300,24 @@
         <v>0.08567595987865505</v>
       </c>
       <c r="S44" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F45">
         <v>0.3740756302521008</v>
@@ -7719,13 +7344,13 @@
         <v>1.304461201119753</v>
       </c>
       <c r="N45" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O45">
         <v>0.009599999999999999</v>
       </c>
       <c r="P45" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q45">
         <v>-0.1507495494343032</v>
@@ -7734,24 +7359,24 @@
         <v>-0.01798994636401634</v>
       </c>
       <c r="S45" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F46">
         <v>0.4805271090386144</v>
@@ -7778,39 +7403,33 @@
         <v>1.353950574887211</v>
       </c>
       <c r="N46" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O46">
         <v>0.0058</v>
       </c>
       <c r="P46" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q46">
-        <v>-0.1735680846859624</v>
-      </c>
-      <c r="R46">
-        <v>-0.02302037088749732</v>
+        <v>110</v>
       </c>
       <c r="S46" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F47">
         <v>0.29</v>
@@ -7831,13 +7450,13 @@
         <v>0.0716</v>
       </c>
       <c r="N47" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O47">
         <v>0.125</v>
       </c>
       <c r="P47" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q47">
         <v>-0.1748543278868911</v>
@@ -7846,24 +7465,24 @@
         <v>0.01485432788689105</v>
       </c>
       <c r="S47" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:19">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F48">
         <v>0.4812407527715649</v>
@@ -7884,39 +7503,33 @@
         <v>0.0042</v>
       </c>
       <c r="N48" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O48">
         <v>0.0114</v>
       </c>
       <c r="P48" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q48">
-        <v>-0.173472335352231</v>
-      </c>
-      <c r="R48">
-        <v>-0.02353042056685119</v>
+        <v>110</v>
       </c>
       <c r="S48" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
         <v>94</v>
       </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F49">
         <v>0.7394957983193278</v>
@@ -7943,39 +7556,33 @@
         <v>1.288243537854977</v>
       </c>
       <c r="N49" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O49">
         <v>0.03154180083166726</v>
       </c>
       <c r="P49" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q49">
-        <v>0.008498016588532281</v>
-      </c>
-      <c r="R49">
-        <v>0.1965811965811965</v>
+        <v>111</v>
       </c>
       <c r="S49" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F50">
         <v>0.01974789915966386</v>
@@ -8002,13 +7609,13 @@
         <v>1.371244234613271</v>
       </c>
       <c r="N50" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O50">
         <v>0.9704</v>
       </c>
       <c r="P50" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q50">
         <v>-0.07491254037785042</v>
@@ -8017,24 +7624,24 @@
         <v>0.09180329668037143</v>
       </c>
       <c r="S50" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F51">
         <v>0.3876470588235295</v>
@@ -8061,13 +7668,13 @@
         <v>1.348689562693561</v>
       </c>
       <c r="N51" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O51">
         <v>0.0308</v>
       </c>
       <c r="P51" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q51">
         <v>-0.1394101766616208</v>
@@ -8076,24 +7683,24 @@
         <v>-0.002186461993842218</v>
       </c>
       <c r="S51" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F52">
         <v>0.4957262730732819</v>
@@ -8120,39 +7727,33 @@
         <v>1.450093471617067</v>
       </c>
       <c r="N52" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O52">
         <v>0.0178</v>
       </c>
       <c r="P52" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q52">
-        <v>-0.157354026556972</v>
-      </c>
-      <c r="R52">
-        <v>-0.01043630456801225</v>
+        <v>110</v>
       </c>
       <c r="S52" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F53">
         <v>0.335</v>
@@ -8173,13 +7774,13 @@
         <v>0.454</v>
       </c>
       <c r="N53" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O53">
         <v>0.4868</v>
       </c>
       <c r="P53" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q53">
         <v>-0.145</v>
@@ -8188,24 +7789,24 @@
         <v>0.07500000000000001</v>
       </c>
       <c r="S53" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F54">
         <v>0.4963766811552734</v>
@@ -8226,39 +7827,33 @@
         <v>0.0078</v>
       </c>
       <c r="N54" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O54">
         <v>0.0204</v>
       </c>
       <c r="P54" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q54">
-        <v>-0.1571408854458069</v>
-      </c>
-      <c r="R54">
-        <v>-0.009901327367602573</v>
+        <v>110</v>
       </c>
       <c r="S54" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
         <v>94</v>
       </c>
-      <c r="C55" t="s">
-        <v>100</v>
-      </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F55">
         <v>0.6764705882352942</v>
@@ -8285,39 +7880,33 @@
         <v>1.324906792740472</v>
       </c>
       <c r="N55" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O55">
         <v>0.3611297063274773</v>
       </c>
       <c r="P55" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q55">
-        <v>-0.0595744680851064</v>
-      </c>
-      <c r="R55">
-        <v>0.1346938775510204</v>
+        <v>111</v>
       </c>
       <c r="S55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F56">
         <v>0.03606060606060607</v>
@@ -8344,13 +7933,13 @@
         <v>1.546875</v>
       </c>
       <c r="N56" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O56">
         <v>0.6018</v>
       </c>
       <c r="P56" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q56">
         <v>-0.1041717788624654</v>
@@ -8359,24 +7948,24 @@
         <v>0.06619198088266737</v>
       </c>
       <c r="S56" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:19">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F57">
         <v>0.4552525252525252</v>
@@ -8403,13 +7992,13 @@
         <v>1.546875</v>
       </c>
       <c r="N57" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O57">
         <v>0.6848</v>
       </c>
       <c r="P57" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q57">
         <v>-0.09169388423036738</v>
@@ -8418,24 +8007,24 @@
         <v>0.06583529837178102</v>
       </c>
       <c r="S57" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F58">
         <v>0.543478322353971</v>
@@ -8462,39 +8051,33 @@
         <v>1.546875</v>
       </c>
       <c r="N58" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O58">
         <v>0.6614</v>
       </c>
       <c r="P58" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q58">
-        <v>-0.09287133053075676</v>
-      </c>
-      <c r="R58">
-        <v>0.06492253544918662</v>
+        <v>110</v>
       </c>
       <c r="S58" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E59" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F59">
         <v>0.45</v>
@@ -8515,13 +8098,13 @@
         <v>0.9892</v>
       </c>
       <c r="N59" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O59">
         <v>0.9892</v>
       </c>
       <c r="P59" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q59">
         <v>-0.114656049457789</v>
@@ -8530,24 +8113,24 @@
         <v>0.134656049457789</v>
       </c>
       <c r="S59" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:19">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F60">
         <v>0.5450403807953941</v>
@@ -8568,39 +8151,33 @@
         <v>0.6748</v>
       </c>
       <c r="N60" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O60">
         <v>0.6748</v>
       </c>
       <c r="P60" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q60">
-        <v>-0.09379365909437119</v>
-      </c>
-      <c r="R60">
-        <v>0.06854289563696495</v>
+        <v>110</v>
       </c>
       <c r="S60" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s">
         <v>94</v>
       </c>
-      <c r="C61" t="s">
-        <v>100</v>
-      </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F61">
         <v>0.5959595959595959</v>
@@ -8627,39 +8204,33 @@
         <v>1.546875</v>
       </c>
       <c r="N61" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O61">
         <v>0.7329150910757301</v>
       </c>
       <c r="P61" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q61">
-        <v>-0.1254247572815532</v>
-      </c>
-      <c r="R61">
-        <v>0.1601320754716982</v>
+        <v>111</v>
       </c>
       <c r="S61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:19">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F62">
         <v>0.03606060606060607</v>
@@ -8686,13 +8257,13 @@
         <v>1.52467233255561</v>
       </c>
       <c r="N62" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O62">
         <v>0.2266</v>
       </c>
       <c r="P62" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q62">
         <v>-0.1930728623380932</v>
@@ -8701,24 +8272,24 @@
         <v>0.03529508456031522</v>
       </c>
       <c r="S62" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" spans="1:19">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F63">
         <v>0.4552525252525252</v>
@@ -8745,13 +8316,13 @@
         <v>1.546875</v>
       </c>
       <c r="N63" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O63">
         <v>0.119</v>
       </c>
       <c r="P63" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q63">
         <v>-0.1428151845382822</v>
@@ -8760,24 +8331,24 @@
         <v>0.01372427544737288</v>
       </c>
       <c r="S63" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F64">
         <v>0.543478322353971</v>
@@ -8804,39 +8375,33 @@
         <v>1.546875</v>
       </c>
       <c r="N64" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O64">
         <v>0.0764</v>
       </c>
       <c r="P64" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q64">
-        <v>-0.1608339457403495</v>
-      </c>
-      <c r="R64">
-        <v>-0.004960680388902138</v>
+        <v>110</v>
       </c>
       <c r="S64" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:19">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E65" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F65">
         <v>0.45</v>
@@ -8857,13 +8422,13 @@
         <v>0.6532</v>
       </c>
       <c r="N65" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O65">
         <v>0.7156</v>
       </c>
       <c r="P65" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q65">
         <v>-0.14</v>
@@ -8872,24 +8437,24 @@
         <v>0.06000000000000004</v>
       </c>
       <c r="S65" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:19">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E66" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F66">
         <v>0.5450403807953941</v>
@@ -8910,39 +8475,33 @@
         <v>0.029</v>
       </c>
       <c r="N66" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O66">
         <v>0.0992</v>
       </c>
       <c r="P66" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q66">
-        <v>-0.1432527526244144</v>
-      </c>
-      <c r="R66">
-        <v>0.001523501976089357</v>
+        <v>110</v>
       </c>
       <c r="S66" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:19">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" t="s">
         <v>94</v>
       </c>
-      <c r="C67" t="s">
-        <v>100</v>
-      </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F67">
         <v>0.5959595959595959</v>
@@ -8969,39 +8528,33 @@
         <v>1.546875</v>
       </c>
       <c r="N67" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O67">
         <v>0.6241432383943554</v>
       </c>
       <c r="P67" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q67">
-        <v>-0.06122448979591832</v>
-      </c>
-      <c r="R67">
-        <v>0.2</v>
+        <v>111</v>
       </c>
       <c r="S67" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:19">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F68">
         <v>0.05505050505050505</v>
@@ -9028,13 +8581,13 @@
         <v>1.210705736991787</v>
       </c>
       <c r="N68" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O68">
         <v>0.4524</v>
       </c>
       <c r="P68" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q68">
         <v>-0.1906136501021066</v>
@@ -9043,24 +8596,24 @@
         <v>0.07081567030412667</v>
       </c>
       <c r="S68" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:19">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F69">
         <v>0.4681818181818182</v>
@@ -9087,13 +8640,13 @@
         <v>1.277004435911887</v>
       </c>
       <c r="N69" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O69">
         <v>0.3428</v>
       </c>
       <c r="P69" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q69">
         <v>-0.1526720041364751</v>
@@ -9102,24 +8655,24 @@
         <v>0.04943968090415207</v>
       </c>
       <c r="S69" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:19">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E70" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F70">
         <v>0.559177787452075</v>
@@ -9146,39 +8699,33 @@
         <v>1.35389219565621</v>
       </c>
       <c r="N70" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O70">
         <v>0.2464</v>
       </c>
       <c r="P70" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q70">
-        <v>-0.1757994104417805</v>
-      </c>
-      <c r="R70">
-        <v>0.02953438105763693</v>
+        <v>110</v>
       </c>
       <c r="S70" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:19">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D71" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F71">
         <v>0.44</v>
@@ -9199,13 +8746,13 @@
         <v>0.6528</v>
       </c>
       <c r="N71" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O71">
         <v>0.7156</v>
       </c>
       <c r="P71" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q71">
         <v>-0.1935531761552672</v>
@@ -9214,24 +8761,24 @@
         <v>0.09355317615526718</v>
       </c>
       <c r="S71" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:19">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D72" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F72">
         <v>0.5592932379303726</v>
@@ -9252,39 +8799,33 @@
         <v>0.148</v>
       </c>
       <c r="N72" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O72">
         <v>0.2186</v>
       </c>
       <c r="P72" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q72">
-        <v>-0.1521339969166954</v>
-      </c>
-      <c r="R72">
-        <v>0.03162738926570315</v>
+        <v>110</v>
       </c>
       <c r="S72" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:19">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" t="s">
         <v>94</v>
       </c>
-      <c r="C73" t="s">
-        <v>100</v>
-      </c>
       <c r="D73" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E73" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F73">
         <v>0.5757575757575758</v>
@@ -9311,22 +8852,16 @@
         <v>1.393609099133894</v>
       </c>
       <c r="N73" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O73">
         <v>0.7329150910757301</v>
       </c>
       <c r="P73" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q73">
-        <v>-0.09999999999999998</v>
-      </c>
-      <c r="R73">
-        <v>0.2021276595744681</v>
+        <v>111</v>
       </c>
       <c r="S73" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -9350,75 +8885,75 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>121</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>122</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>124</v>
       </c>
-      <c r="H1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>125</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>126</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>127</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>128</v>
-      </c>
-      <c r="N1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" t="s">
-        <v>130</v>
-      </c>
-      <c r="P1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>132</v>
-      </c>
-      <c r="R1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
         <v>134</v>
       </c>
-      <c r="D2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" t="s">
-        <v>139</v>
-      </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H2">
         <v>406</v>
@@ -9442,36 +8977,36 @@
         <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="P2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" t="s">
         <v>135</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" t="s">
-        <v>140</v>
       </c>
       <c r="H3">
         <v>69</v>
@@ -9495,36 +9030,36 @@
         <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="P3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H4">
         <v>238</v>
@@ -9548,36 +9083,36 @@
         <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="P4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H5">
         <v>99</v>
@@ -9601,16 +9136,16 @@
         <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
